--- a/workspaces/btc_daily_14days/rsi/rsi_21.xlsx
+++ b/workspaces/btc_daily_14days/rsi/rsi_21.xlsx
@@ -572,49 +572,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>1.673228346455744</v>
+        <v>1.742536164285497</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>2.145484166398688</v>
+        <v>2.227405304656358</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>5.919703169607409</v>
+        <v>6.160557691785158</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-6.457705556779935</v>
+        <v>-6.718871244308126</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-2.827362130533118</v>
+        <v>-2.936626529617506</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-6.702036786196359</v>
+        <v>-6.969438058989702</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-6.788703888814503</v>
+        <v>-7.064748409883876</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-15.60619853201133</v>
+        <v>-16.24331809846158</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-9.408927642340878</v>
+        <v>-9.795687661434542</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-10.26334815600936</v>
+        <v>-10.68594478252574</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-9.291900819197735</v>
+        <v>-9.674987373443876</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-5.081674721455791</v>
+        <v>-5.29656648471547</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-8.485655154974701</v>
+        <v>-8.838186793179148</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-6.154178788350386</v>
+        <v>-6.414552417424602</v>
       </c>
     </row>
     <row r="7">
@@ -624,49 +624,49 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>1.474815648043993</v>
+        <v>1.495786985219439</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-3.312224194996254</v>
+        <v>-3.359664405500567</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-2.119974777251393</v>
+        <v>-2.148737154838187</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-6.755681986233299</v>
+        <v>-6.849165590451449</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-7.296218716432541</v>
+        <v>-7.395402691992608</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-13.35745988004297</v>
+        <v>-13.54099019346938</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-15.03555904070615</v>
+        <v>-15.24405371467541</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-13.91747092023321</v>
+        <v>-14.11212182028589</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-7.620136500988565</v>
+        <v>-7.727738145787811</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-5.292418933791488</v>
+        <v>-5.368279032873723</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-15.0430446486993</v>
+        <v>-15.25365429972066</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-6.155638451932425</v>
+        <v>-6.244019138755988</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-4.979232833153468</v>
+        <v>-5.051370523894441</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-6.323124120710922</v>
+        <v>-6.414552417424602</v>
       </c>
     </row>
     <row r="8">
@@ -676,49 +676,49 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-6.243438320209123</v>
+        <v>-6.56023135943569</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-5.356431503214417</v>
+        <v>-5.639971940229998</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.500379916829047</v>
+        <v>0.5264012929987061</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-3.12211828536504</v>
+        <v>-3.287951676167225</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-2.410513909156009</v>
+        <v>-2.533611071819195</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.1767225933326415</v>
+        <v>-0.1921903877948452</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.992774361404912</v>
+        <v>1.029288531107902</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>2.478776813622673</v>
+        <v>2.586308866828823</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-5.64959348904906</v>
+        <v>-5.953891425035287</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-7.015313953174726</v>
+        <v>-7.389438445468052</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-3.448028242611073</v>
+        <v>-3.646823348733598</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-5.923008089827114</v>
+        <v>-6.244019138755988</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-6.323583862523833</v>
+        <v>-6.664273749700889</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.1755613970424363</v>
+        <v>0.1643949509970497</v>
       </c>
     </row>
     <row r="9">
@@ -728,49 +728,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>3.062117235345326</v>
+        <v>3.20087317539236</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>1.450849664499231</v>
+        <v>1.504691725406609</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-3.895539793785261</v>
+        <v>-4.074848232170851</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-4.269734460807477</v>
+        <v>-4.475390073190965</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-1.965887445747747</v>
+        <v>-2.058598888689986</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-2.786649884331915</v>
+        <v>-2.921556919895735</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-5.58748157850431</v>
+        <v>-5.85813119946706</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-4.919404239103621</v>
+        <v>-5.162523900573611</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-7.197530161980957</v>
+        <v>-7.549105182104746</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-9.120432060047044</v>
+        <v>-9.562021064807098</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.6899402324419484</v>
+        <v>0.698341889945624</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-2.613294433691799</v>
+        <v>-2.755647045732736</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-1.903968672377374</v>
+        <v>-2.013110959003221</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-1.667880218314366</v>
+        <v>-1.763389626727985</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>112</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-2.493438320209975</v>
+        <v>-2.492765811613864</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.5337979876879686</v>
+        <v>-0.5335833617460608</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-2.714921613592054</v>
+        <v>-2.714166354055934</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-1.691590863374095</v>
+        <v>-1.691056078591494</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-3.123203620727921</v>
+        <v>-3.1223344365212</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-5.505008776427488</v>
+        <v>-5.503463927376565</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-4.696721838424388</v>
+        <v>-4.695340501791911</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-6.057146621530933</v>
+        <v>-6.055381043430756</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-3.438899414298014</v>
+        <v>-3.437809501041222</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-6.075471766515655</v>
+        <v>-6.07364897178384</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-6.280239331417057</v>
+        <v>-6.278402296101419</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-6.245856174071626</v>
+        <v>-6.244019138755988</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-3.986920653936188</v>
+        <v>-3.985702321129061</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.7283810142744471</v>
+        <v>0.7283047254329489</v>
       </c>
     </row>
     <row r="11">
@@ -832,49 +832,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-9.273099337159323</v>
+        <v>-9.352916057023442</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-1.101724936094229</v>
+        <v>-1.113558941721443</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>2.742989881925133</v>
+        <v>2.765076625186254</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>2.873702092337133</v>
+        <v>2.895329757793753</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>5.728324930371286</v>
+        <v>5.77571196152519</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>3.48247583112181</v>
+        <v>3.509051335138096</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>5.094952757109361</v>
+        <v>5.13371932726772</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>3.785132048156449</v>
+        <v>3.811835073785367</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.512237818010064</v>
+        <v>-0.5226690859016045</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-1.35387006365449</v>
+        <v>-1.372794270929333</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>1.831666198307012</v>
+        <v>1.841255823556708</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>1.866049355652443</v>
+        <v>1.875638980902139</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>1.448549211534591</v>
+        <v>1.455384369956846</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.000546871764640855</v>
+        <v>-0.004296007168193228</v>
       </c>
     </row>
     <row r="12">
@@ -2213,10 +2213,8 @@
           <t>X &gt; 23.64</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>4074~4086</t>
-        </is>
+      <c r="B6" t="n">
+        <v>4074</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>-0.02158320518305601</v>
@@ -2267,10 +2265,8 @@
           <t>X &gt; 25.79</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>4028~4038</t>
-        </is>
+      <c r="B7" t="n">
+        <v>4028</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>-0.04172955349377361</v>
@@ -2321,10 +2317,8 @@
           <t>X &gt; 27.94</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>3966~3975</t>
-        </is>
+      <c r="B8" t="n">
+        <v>3966</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>-0.06576536423512636</v>
@@ -2375,10 +2369,8 @@
           <t>X &gt; 30.1</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>3890~3895</t>
-        </is>
+      <c r="B9" t="n">
+        <v>3890</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>0.06111880430863437</v>
@@ -2429,10 +2421,8 @@
           <t>X &gt; 32.25</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>3804~3805</t>
-        </is>
+      <c r="B10" t="n">
+        <v>3804</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>-0.009864075794730809</v>
@@ -2483,10 +2473,8 @@
           <t>X &gt; 34.41</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>3692~3693</t>
-        </is>
+      <c r="B11" t="n">
+        <v>3692</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>0.06545688693868357</v>
@@ -2537,10 +2525,8 @@
           <t>X &gt; 36.56</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>3575~3575</t>
-        </is>
+      <c r="B12" t="n">
+        <v>3575</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>0.3736945469228985</v>
@@ -2591,10 +2577,8 @@
           <t>X &gt; 38.71</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>3403~3403</t>
-        </is>
+      <c r="B13" t="n">
+        <v>3403</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>0.4304523644800042</v>
@@ -2645,10 +2629,8 @@
           <t>X &gt; 40.87</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>3236~3236</t>
-        </is>
+      <c r="B14" t="n">
+        <v>3236</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>0.1641636575403354</v>
@@ -2699,10 +2681,8 @@
           <t>X &gt; 43.02</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>3042~3042</t>
-        </is>
+      <c r="B15" t="n">
+        <v>3042</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>-0.1923206344769071</v>
@@ -2753,10 +2733,8 @@
           <t>X &gt; 45.18</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2853~2853</t>
-        </is>
+      <c r="B16" t="n">
+        <v>2853</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>-0.4780159577844643</v>
@@ -2807,10 +2785,8 @@
           <t>X &gt; 47.33</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2618~2618</t>
-        </is>
+      <c r="B17" t="n">
+        <v>2618</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>0.4477381503782638</v>
@@ -2861,10 +2837,8 @@
           <t>X &gt; 49.48</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2399~2399</t>
-        </is>
+      <c r="B18" t="n">
+        <v>2399</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>1.153914743566595</v>
@@ -2915,10 +2889,8 @@
           <t>X &gt; 51.64</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2204~2204</t>
-        </is>
+      <c r="B19" t="n">
+        <v>2204</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>1.453930100842655</v>
@@ -2969,10 +2941,8 @@
           <t>X &gt; 53.79</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>1967~1967</t>
-        </is>
+      <c r="B20" t="n">
+        <v>1967</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>1.904121415428051</v>
@@ -3023,10 +2993,8 @@
           <t>X &gt; 55.94</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>1760~1760</t>
-        </is>
+      <c r="B21" t="n">
+        <v>1760</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>1.881561679790018</v>
@@ -3077,10 +3045,8 @@
           <t>X &gt; 58.1</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>1555~1555</t>
-        </is>
+      <c r="B22" t="n">
+        <v>1555</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>2.23324978268392</v>
@@ -3131,10 +3097,8 @@
           <t>X &gt; 60.25</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>1383~1383</t>
-        </is>
+      <c r="B23" t="n">
+        <v>1383</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>2.242642663159508</v>
@@ -3185,10 +3149,8 @@
           <t>X &gt; 62.41</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>1226~1226</t>
-        </is>
+      <c r="B24" t="n">
+        <v>1226</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>2.482091859235375</v>
@@ -3239,10 +3201,8 @@
           <t>X &gt; 64.56</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>1057~1057</t>
-        </is>
+      <c r="B25" t="n">
+        <v>1057</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>2.568056476384157</v>
@@ -3293,10 +3253,8 @@
           <t>X &gt; 66.71</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>908~908</t>
-        </is>
+      <c r="B26" t="n">
+        <v>908</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>3.784094719437604</v>
@@ -3347,10 +3305,8 @@
           <t>X &gt; 68.87</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>765~765</t>
-        </is>
+      <c r="B27" t="n">
+        <v>765</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>4.238587823580872</v>
@@ -3401,10 +3357,8 @@
           <t>X &gt; 71.02</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>624~624</t>
-        </is>
+      <c r="B28" t="n">
+        <v>624</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>3.596305269533616</v>
@@ -3455,10 +3409,8 @@
           <t>X &gt; 73.18</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>515~515</t>
-        </is>
+      <c r="B29" t="n">
+        <v>515</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>5.370639349692937</v>
@@ -3509,10 +3461,8 @@
           <t>X &gt; 75.33</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>420~420</t>
-        </is>
+      <c r="B30" t="n">
+        <v>420</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>5.125609298837638</v>
@@ -3563,10 +3513,8 @@
           <t>X &gt; 77.48</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>310~310</t>
-        </is>
+      <c r="B31" t="n">
+        <v>310</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>5.571077808822288</v>
@@ -3617,10 +3565,8 @@
           <t>X &gt; 79.64</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>232~232</t>
-        </is>
+      <c r="B32" t="n">
+        <v>232</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>5.265182369445199</v>
@@ -3671,10 +3617,8 @@
           <t>X &gt; 81.79</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>184~184</t>
-        </is>
+      <c r="B33" t="n">
+        <v>184</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>4.028300810224806</v>
@@ -3725,10 +3669,8 @@
           <t>X &gt; 83.95</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>129~129</t>
-        </is>
+      <c r="B34" t="n">
+        <v>129</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>1.77012757126289</v>
@@ -3779,10 +3721,8 @@
           <t>X &gt; 86.1</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>84~84</t>
-        </is>
+      <c r="B35" t="n">
+        <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>3.458942632170981</v>
@@ -3967,10 +3907,8 @@
           <t>X &lt; 23.64</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>83~84</t>
-        </is>
+      <c r="B6" t="n">
+        <v>83</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>1.077990251218594</v>
@@ -4021,10 +3959,8 @@
           <t>X &lt; 25.79</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>129~132</t>
-        </is>
+      <c r="B7" t="n">
+        <v>129</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>1.294440467668807</v>
@@ -4075,10 +4011,8 @@
           <t>X &lt; 27.94</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>191~195</t>
-        </is>
+      <c r="B8" t="n">
+        <v>191</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>1.352715525943871</v>
@@ -4129,10 +4063,8 @@
           <t>X &lt; 30.1</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>267~275</t>
-        </is>
+      <c r="B9" t="n">
+        <v>267</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>-0.8570746838463421</v>
@@ -4183,10 +4115,8 @@
           <t>X &lt; 32.25</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>353~365</t>
-        </is>
+      <c r="B10" t="n">
+        <v>353</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>0.1093014058174191</v>
@@ -4237,10 +4167,8 @@
           <t>X &lt; 34.41</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>465~477</t>
-        </is>
+      <c r="B11" t="n">
+        <v>465</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>-0.5018240644447829</v>
@@ -4291,10 +4219,8 @@
           <t>X &lt; 36.56</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>582~595</t>
-        </is>
+      <c r="B12" t="n">
+        <v>582</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>-2.241337479873842</v>
@@ -4345,10 +4271,8 @@
           <t>X &lt; 38.71</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>754~767</t>
-        </is>
+      <c r="B13" t="n">
+        <v>754</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>-1.906736886050908</v>
@@ -4399,10 +4323,8 @@
           <t>X &lt; 40.87</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>921~934</t>
-        </is>
+      <c r="B14" t="n">
+        <v>921</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>-0.5662434593962686</v>
@@ -4453,10 +4375,8 @@
           <t>X &lt; 43.02</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>1115~1128</t>
-        </is>
+      <c r="B15" t="n">
+        <v>1115</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>0.5207460769531451</v>
@@ -4507,10 +4427,8 @@
           <t>X &lt; 45.18</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>1304~1317</t>
-        </is>
+      <c r="B16" t="n">
+        <v>1304</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>1.037313388218273</v>
@@ -4561,10 +4479,8 @@
           <t>X &lt; 47.33</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1539~1552</t>
-        </is>
+      <c r="B17" t="n">
+        <v>1539</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>-0.7537475985604871</v>
@@ -4615,10 +4531,8 @@
           <t>X &lt; 49.48</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>1758~1771</t>
-        </is>
+      <c r="B18" t="n">
+        <v>1758</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>-1.561761301576439</v>
@@ -4669,10 +4583,8 @@
           <t>X &lt; 51.64</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>1953~1966</t>
-        </is>
+      <c r="B19" t="n">
+        <v>1953</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>-1.628738421939374</v>
@@ -4723,10 +4635,8 @@
           <t>X &lt; 53.79</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2190~2203</t>
-        </is>
+      <c r="B20" t="n">
+        <v>2190</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>-1.699067008362491</v>
@@ -4777,10 +4687,8 @@
           <t>X &lt; 55.94</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2397~2410</t>
-        </is>
+      <c r="B21" t="n">
+        <v>2397</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>-1.37310637000251</v>
@@ -4831,10 +4739,8 @@
           <t>X &lt; 58.1</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2602~2615</t>
-        </is>
+      <c r="B22" t="n">
+        <v>2602</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>-1.327090327858166</v>
@@ -4885,10 +4791,8 @@
           <t>X &lt; 60.25</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2774~2787</t>
-        </is>
+      <c r="B23" t="n">
+        <v>2774</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>-1.112024613715533</v>
@@ -4939,10 +4843,8 @@
           <t>X &lt; 62.41</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2931~2944</t>
-        </is>
+      <c r="B24" t="n">
+        <v>2931</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>-1.032840494123022</v>
@@ -4993,10 +4895,8 @@
           <t>X &lt; 64.56</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>3100~3113</t>
-        </is>
+      <c r="B25" t="n">
+        <v>3100</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>-0.8712089594647097</v>
@@ -5047,10 +4947,8 @@
           <t>X &lt; 66.71</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>3249~3262</t>
-        </is>
+      <c r="B26" t="n">
+        <v>3249</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>-1.052604475942658</v>
@@ -5101,10 +4999,8 @@
           <t>X &lt; 68.87</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>3392~3405</t>
-        </is>
+      <c r="B27" t="n">
+        <v>3392</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>-0.9515880999456598</v>
@@ -5155,10 +5051,8 @@
           <t>X &lt; 71.02</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>3533~3546</t>
-        </is>
+      <c r="B28" t="n">
+        <v>3533</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>-0.6321862051507523</v>
@@ -5209,10 +5103,8 @@
           <t>X &lt; 73.18</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>3642~3655</t>
-        </is>
+      <c r="B29" t="n">
+        <v>3642</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>-0.7560922189787931</v>
@@ -5263,10 +5155,8 @@
           <t>X &lt; 75.33</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>3737~3750</t>
-        </is>
+      <c r="B30" t="n">
+        <v>3737</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>-0.5734383202099735</v>
@@ -5317,10 +5207,8 @@
           <t>X &lt; 77.48</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>3847~3860</t>
-        </is>
+      <c r="B31" t="n">
+        <v>3847</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>-0.4468061958576399</v>
@@ -5371,10 +5259,8 @@
           <t>X &lt; 79.64</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>3925~3938</t>
-        </is>
+      <c r="B32" t="n">
+        <v>3925</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>-0.3095886503267877</v>
@@ -5425,10 +5311,8 @@
           <t>X &lt; 81.79</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>3973~3986</t>
-        </is>
+      <c r="B33" t="n">
+        <v>3973</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>-0.1853600462511196</v>
@@ -5479,10 +5363,8 @@
           <t>X &lt; 83.95</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>4028~4041</t>
-        </is>
+      <c r="B34" t="n">
+        <v>4028</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>-0.05592285374127925</v>
@@ -5533,10 +5415,8 @@
           <t>X &lt; 86.1</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>4073~4086</t>
-        </is>
+      <c r="B35" t="n">
+        <v>4073</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>-0.07053083122319492</v>

--- a/workspaces/btc_daily_14days/rsi/rsi_21.xlsx
+++ b/workspaces/btc_daily_14days/rsi/rsi_21.xlsx
@@ -479,7 +479,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that RSI-21 is approximately at value x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that RSI-21 is approximately at value x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -568,105 +568,105 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ 24.71</t>
+          <t>X ≈ 24.72</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>46</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>1.742536164285497</v>
+        <v>1.75514340211469</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>2.227405304656358</v>
+        <v>2.240341652484091</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>6.160557691785158</v>
+        <v>6.172595558227343</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-6.718871244308126</v>
+        <v>-6.703694476650369</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-2.936626529617506</v>
+        <v>-2.922267705326163</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-6.969438058989702</v>
+        <v>-6.954148706630903</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-7.064748409883876</v>
+        <v>-7.04937498255822</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-16.24331809846158</v>
+        <v>-16.22554148665799</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-9.795687661434542</v>
+        <v>-9.779468134328091</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-10.68594478252574</v>
+        <v>-10.66927908217006</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-9.674987373443876</v>
+        <v>-10.88572141533896</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-5.29656648471547</v>
+        <v>-5.281459219266999</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-8.838186793179148</v>
+        <v>-10.0590932701678</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-6.414552417424602</v>
+        <v>-6.424982053122754</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ 26.87</t>
+          <t>X ≈ 26.88</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>62</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>1.495786985219439</v>
+        <v>1.508098843637519</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-3.359664405500567</v>
+        <v>-3.345693914548363</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-2.148737154838187</v>
+        <v>-2.135009406223745</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-6.849165590451449</v>
+        <v>-6.834268187181721</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-7.395402691992608</v>
+        <v>-7.380263002543337</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-13.54099019346938</v>
+        <v>-13.52435813008601</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-15.24405371467541</v>
+        <v>-15.22693211608629</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-14.11212182028589</v>
+        <v>-14.09513446955871</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-7.727738145787811</v>
+        <v>-7.712336723831427</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-5.368279032873723</v>
+        <v>-5.353250297293457</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-15.25365429972066</v>
+        <v>-15.24019700601044</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-6.244019138755988</v>
+        <v>-7.141302724622861</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-5.051370523894441</v>
+        <v>-5.037814477542838</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-6.414552417424602</v>
+        <v>-6.424982053122754</v>
       </c>
     </row>
     <row r="8">
@@ -676,49 +676,49 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-6.56023135943569</v>
+        <v>-5.84418317486994</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-5.639971940229998</v>
+        <v>-4.95637361007487</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.5264012929987061</v>
+        <v>-0.1739293093770229</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-3.287951676167225</v>
+        <v>-3.936261686332919</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-2.533611071819195</v>
+        <v>-3.198970480477193</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.1921903877948452</v>
+        <v>-1.595653222558056</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>1.029288531107902</v>
+        <v>0.3191877406897206</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>2.586308866828823</v>
+        <v>1.128695019413286</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-5.953891425035287</v>
+        <v>-7.301077037746673</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-7.389438445468052</v>
+        <v>-8.739981550337326</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-3.646823348733598</v>
+        <v>-4.316893054338657</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-6.244019138755988</v>
+        <v>-6.87991749938594</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-6.664273749700889</v>
+        <v>-7.300068352699348</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.1643949509970497</v>
+        <v>-0.5808262089675011</v>
       </c>
     </row>
     <row r="9">
@@ -728,49 +728,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>3.20087317539236</v>
+        <v>2.692804792995005</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>1.504691725406609</v>
+        <v>0.9963812416603162</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-4.074848232170851</v>
+        <v>-4.109574887904103</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-4.475390073190965</v>
+        <v>-4.517158612030066</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-2.058598888689986</v>
+        <v>-2.070168842921404</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-2.921556919895735</v>
+        <v>-2.300573112481501</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-5.85813119946706</v>
+        <v>-5.917114713241219</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-5.162523900573611</v>
+        <v>-4.561107597161261</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-7.549105182104746</v>
+        <v>-6.975030930154091</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-9.562021064807098</v>
+        <v>-9.001420314719248</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.698341889945624</v>
+        <v>1.382113821137672</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-2.755647045732736</v>
+        <v>-2.112919791212882</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-2.013110959003221</v>
+        <v>-1.356600056290993</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-1.763389626727985</v>
+        <v>-1.130864406063928</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>112</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-2.492765811613864</v>
+        <v>-2.479578843446951</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.5335833617460608</v>
+        <v>-0.5204628531422202</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-2.714166354055934</v>
+        <v>-2.701159222638331</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-1.691056078591494</v>
+        <v>-1.67807693619303</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-3.1223344365212</v>
+        <v>-3.109223632146261</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-5.503463927376565</v>
+        <v>-5.490421031082199</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-4.695340501791911</v>
+        <v>-4.682274247491435</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-6.055381043430756</v>
+        <v>-6.042200034135519</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-3.437809501041222</v>
+        <v>-3.424610762086459</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-6.07364897178384</v>
+        <v>-6.060243844131008</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-6.278402296101419</v>
+        <v>-6.264945002391201</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-6.244019138755988</v>
+        <v>-6.230566850035878</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-3.985702321129061</v>
+        <v>-3.972146274777458</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.7283047254329489</v>
+        <v>0.7178750897347967</v>
       </c>
     </row>
     <row r="11">
@@ -835,46 +835,46 @@
         <v>117</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-9.352916057023442</v>
+        <v>-9.337642398584819</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-1.113558941721443</v>
+        <v>-1.565376810520576</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>2.765076625186254</v>
+        <v>2.778083756603856</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>2.895329757793753</v>
+        <v>2.908308900192218</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>5.77571196152519</v>
+        <v>5.788822765900129</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>3.509051335138096</v>
+        <v>3.522094231432462</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>5.13371932726772</v>
+        <v>5.146785581568196</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>3.811835073785367</v>
+        <v>3.825016083080605</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.5226690859016045</v>
+        <v>-0.5094703469468413</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-1.372794270929333</v>
+        <v>-1.359389143276502</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>1.841255823556708</v>
+        <v>1.854713117266925</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>1.875638980902139</v>
+        <v>1.889091269622249</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>1.455384369956846</v>
+        <v>1.468940416308449</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.004296007168193228</v>
+        <v>-0.01472564286634537</v>
       </c>
     </row>
     <row r="12">
@@ -887,98 +887,98 @@
         <v>172</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.749252273698211</v>
+        <v>-0.7364044367409903</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-4.105011933174232</v>
+        <v>-4.092102123598181</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-1.592903895584904</v>
+        <v>-1.579896764167302</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.2998600653028589</v>
+        <v>-0.2868809229043947</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.3245094172993888</v>
+        <v>0.337620221674328</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-1.122234691496445</v>
+        <v>-1.109191795202079</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-1.206968408768979</v>
+        <v>-1.193902154468503</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-1.092756458713147</v>
+        <v>-1.079575449417909</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.5904297016163156</v>
+        <v>0.6036284405710788</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-2.003881529923376</v>
+        <v>-1.990476402270545</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-1.62723950540375</v>
+        <v>-1.613782211693533</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-3.918437743407146</v>
+        <v>-3.904985454687036</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-5.501483052026465</v>
+        <v>-5.487927005674862</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-9.90292451044786</v>
+        <v>-9.913354146146013</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ 39.79</t>
+          <t>X ≈ 39.8</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>5.590394015119372</v>
+        <v>6.097212445889518</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-2.60800594515014</v>
+        <v>-2.612812182769652</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>5.979161276397122</v>
+        <v>5.868156077445597</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>5.510612013794898</v>
+        <v>5.406665244702737</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>7.966202774770494</v>
+        <v>7.826955573263838</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>4.670830341228672</v>
+        <v>4.574033744910629</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>6.981306204794713</v>
+        <v>6.856187290969906</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>5.316518015593921</v>
+        <v>5.205686694520445</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>4.057913338992314</v>
+        <v>3.961272585334818</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>2.608985758755082</v>
+        <v>2.519637812673857</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>1.805430039227929</v>
+        <v>1.723220678082171</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-1.753001174684137</v>
+        <v>-1.792697027550673</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-2.173255785628889</v>
+        <v>-1.621131904532717</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.4716751274855824</v>
+        <v>0.3797516746878955</v>
       </c>
     </row>
     <row r="14">
@@ -988,101 +988,101 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>5.753984360202402</v>
+        <v>5.277570727800438</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>2.080555077135045</v>
+        <v>2.384581814225655</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.3761692995646371</v>
+        <v>-0.0827284306328977</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>1.815939503145955</v>
+        <v>2.120035573058978</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>2.308446123125329</v>
+        <v>2.61801545001498</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>2.090424143315218</v>
+        <v>2.397254764624279</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-2.63348483168901</v>
+        <v>-2.35066802987506</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-3.100668230470404</v>
+        <v>-2.817736673661798</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.5843485290238348</v>
+        <v>-0.2880452550550388</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.1119180385255589</v>
+        <v>0.4164400936929482</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-1.123763120843684</v>
+        <v>-0.8245304946190615</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-2.635771716075574</v>
+        <v>-2.344556487341698</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-2.540562409494818</v>
+        <v>-2.764707340654986</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-5.383624582373059</v>
+        <v>-5.129645265557869</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ 44.1</t>
+          <t>X ≈ 44.11</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>4.120318293546759</v>
+        <v>3.902062692870025</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.1367579649202639</v>
+        <v>-0.3686978682790283</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.002526142416321875</v>
+        <v>-0.2315543594169327</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-5.16327830081412</v>
+        <v>-5.4204781519989</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-4.114397928584701</v>
+        <v>-4.363023024243525</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-4.875157049070097</v>
+        <v>-5.129478781842487</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-5.488991295442908</v>
+        <v>-5.746104034725676</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-8.072576810626522</v>
+        <v>-8.340832252980498</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-4.429872993105121</v>
+        <v>-4.678410154184121</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-5.279998178133049</v>
+        <v>-5.528328950514108</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-8.659354677053805</v>
+        <v>-8.924519470476433</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-1.746664641401487</v>
+        <v>-1.97524770109959</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-4.812421897848921</v>
+        <v>-5.054973022498103</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-5.0918010946734</v>
+        <v>-5.361152265888947</v>
       </c>
     </row>
     <row r="16">
@@ -1095,46 +1095,46 @@
         <v>235</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-10.7913106606356</v>
+        <v>-10.77878837095998</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.788605088102365</v>
+        <v>0.8015148976784161</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-2.584987022749637</v>
+        <v>-2.571979891332035</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-2.029201975248434</v>
+        <v>-2.016222832849969</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-6.82294233925677</v>
+        <v>-6.80983153488183</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-2.69571316749856</v>
+        <v>-2.682670271204195</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-3.631510714558068</v>
+        <v>-3.618444460257592</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-3.673162198445851</v>
+        <v>-3.659981189150614</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-5.436289744202625</v>
+        <v>-5.423091005247862</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-3.733223439868951</v>
+        <v>-3.71981831221612</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-3.512444849292912</v>
+        <v>-3.498987555582694</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-1.775934032373009</v>
+        <v>-1.762481743652899</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>2.484662420511782</v>
+        <v>2.498218466863385</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>3.585447582575497</v>
+        <v>3.575017946877345</v>
       </c>
     </row>
     <row r="17">
@@ -1147,46 +1147,46 @@
         <v>219</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-7.28795886815508</v>
+        <v>-7.275436578479457</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-4.789943440023549</v>
+        <v>-4.777033630447498</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-7.467917169451191</v>
+        <v>-7.454910038033589</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-9.620769059674743</v>
+        <v>-9.607789917276278</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-8.332706256482069</v>
+        <v>-8.31959545210713</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-10.31836934159756</v>
+        <v>-10.30532644530319</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-7.663377031472479</v>
+        <v>-7.650310777172002</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-4.934213398290609</v>
+        <v>-4.921032388995371</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-6.821697302737753</v>
+        <v>-6.80849856378299</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-4.932096460368314</v>
+        <v>-4.918691332715483</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-3.310365766421057</v>
+        <v>-3.29690847271084</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-2.362740599943209</v>
+        <v>-2.349288311223098</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-1.413132197189469</v>
+        <v>-1.399576150837866</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-2.076652874045607</v>
+        <v>-2.087082509743759</v>
       </c>
     </row>
     <row r="18">
@@ -1199,46 +1199,46 @@
         <v>195</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-2.237028063799833</v>
+        <v>-2.224505774124211</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-4.361422189584374</v>
+        <v>-4.348512380008323</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-9.371675511565577</v>
+        <v>-9.358668380147975</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-5.138858276394203</v>
+        <v>-5.125879133995738</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-6.702920517107167</v>
+        <v>-6.689809712732227</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-2.815734989647801</v>
+        <v>-2.802692093353436</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-7.003032809484296</v>
+        <v>-6.98996655518382</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-3.880472618522333</v>
+        <v>-3.867291609227095</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-3.428651991884237</v>
+        <v>-3.415453252929474</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-5.817238715373584</v>
+        <v>-5.803833587720753</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-4.483530501229616</v>
+        <v>-4.470073207519398</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-3.423506318243163</v>
+        <v>-3.410054029523053</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-4.86940195482898</v>
+        <v>-4.855845908477377</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-5.132501135373438</v>
+        <v>-5.14293077107159</v>
       </c>
     </row>
     <row r="19">
@@ -1251,150 +1251,150 @@
         <v>237</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-2.282467856074959</v>
+        <v>-2.269945566399336</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-3.894041469039301</v>
+        <v>-3.88113165946325</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-7.24249667352619</v>
+        <v>-7.229489542108588</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-4.580597971298339</v>
+        <v>-4.567618828899874</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-1.743491760210269</v>
+        <v>-1.730380955835329</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-1.024108894224661</v>
+        <v>-1.011065997930295</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-3.218547252847159</v>
+        <v>-3.205480998546683</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-1.154085082008216</v>
+        <v>-1.140904072712978</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.7931440399202785</v>
+        <v>-0.7799453009655153</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-2.065210153218445</v>
+        <v>-2.051805025565614</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-3.11384533407611</v>
+        <v>-3.100388040365893</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-5.611107746351024</v>
+        <v>-5.597655457630914</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-6.453303285565958</v>
+        <v>-6.439747239214356</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-7.047463809829566</v>
+        <v>-7.057893445527718</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ 54.86</t>
+          <t>X ≈ 54.87</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>207</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>2.095933660466407</v>
+        <v>2.10845595014203</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>3.866002559579393</v>
+        <v>3.878912369155444</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>4.920409215301639</v>
+        <v>4.933416346719241</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>1.185928048392348</v>
+        <v>1.198907190790813</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.284860316438383</v>
+        <v>-1.271749512063444</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.5043265912830108</v>
+        <v>-0.4912836949886454</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>4.241857565840846</v>
+        <v>4.254923820141322</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.5731519198972848</v>
+        <v>-0.559970910602047</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.3320317687995313</v>
+        <v>0.3452305077542945</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>3.346640883288622</v>
+        <v>3.360046010941453</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>2.65879577153143</v>
+        <v>2.672253065241648</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>2.693178928876861</v>
+        <v>2.706631217596971</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.340557168173504</v>
+        <v>0.3541132145251069</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>1.556462075329023</v>
+        <v>1.546032439630871</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 57.02</t>
+          <t>X ≈ 57.03</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>205</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.7861212470393539</v>
+        <v>-0.7735989573637312</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>1.50474416438675</v>
+        <v>1.517653973962801</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>2.085485213887708</v>
+        <v>2.09849234530531</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>2.215738346495208</v>
+        <v>2.228717488893672</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1.677317131423038</v>
+        <v>1.690427935797977</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>2.950368825236261</v>
+        <v>2.963411721530626</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.9144155957688724</v>
+        <v>0.9274818500693485</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.910646831133704</v>
+        <v>1.923827840428942</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-1.077182323341333</v>
+        <v>-1.06398358438657</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-3.390722142515543</v>
+        <v>-3.377317014862712</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.6686461985404364</v>
+        <v>-0.6551889048302186</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-2.585482553390072</v>
+        <v>-2.572030264669962</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-2.517932286286253</v>
+        <v>-2.504376239934651</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-4.21943046620509</v>
+        <v>-4.229860101903242</v>
       </c>
     </row>
     <row r="22">
@@ -1407,46 +1407,46 @@
         <v>172</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>2.157724470487764</v>
+        <v>2.170246760163387</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.6166398401509809</v>
+        <v>-0.6037300305749298</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.1512821509269173</v>
+        <v>0.1642892823445194</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>2.025721330045982</v>
+        <v>2.038700472444447</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.41967662921224</v>
+        <v>-1.406565824837301</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>2.947532750363891</v>
+        <v>2.960575646658256</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.5372176377427706</v>
+        <v>0.5502838920432467</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.511361109875871</v>
+        <v>-0.4981801005806332</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.5723609960581726</v>
+        <v>-0.5591622571034094</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.841090832248959</v>
+        <v>-0.8276857045961279</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.4644488077293261</v>
+        <v>-0.4509915140191083</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-1.011460999221107</v>
+        <v>-0.9980087105009972</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-4.338692354352048</v>
+        <v>-4.325136308000445</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-4.670366370912973</v>
+        <v>-4.680796006611125</v>
       </c>
     </row>
     <row r="23">
@@ -1459,46 +1459,46 @@
         <v>157</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.3728037180065868</v>
+        <v>0.3853260076822096</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.6018272197984373</v>
+        <v>-0.5889174102223862</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.9966959263950912</v>
+        <v>-0.9836887949774891</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-4.688098844742939</v>
+        <v>-4.675119702344475</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-3.315692034337467</v>
+        <v>-3.302581229962527</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-6.839906147577153</v>
+        <v>-6.826863251282788</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.5552131132570821</v>
+        <v>-0.5421468589566061</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.888431513439059</v>
+        <v>0.9016125227342968</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>2.101316977575294</v>
+        <v>2.114515716530057</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>1.888134467706607</v>
+        <v>1.901539595359438</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-2.775217582725624</v>
+        <v>-2.761760289015406</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-4.65166245085782</v>
+        <v>-4.63821016213771</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-3.798031711484327</v>
+        <v>-3.784475665132724</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-3.54831037920804</v>
+        <v>-3.558740014906192</v>
       </c>
     </row>
     <row r="24">
@@ -1511,150 +1511,150 @@
         <v>169</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1.944431502275229</v>
+        <v>1.956953791950852</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.3328578893109722</v>
+        <v>0.3457676988870233</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>4.080001017033908</v>
+        <v>4.09300814845151</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>6.577118054966789</v>
+        <v>6.590097197365253</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>7.22212879255747</v>
+        <v>7.235239596932409</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>9.294718659267154</v>
+        <v>9.30776155556152</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>8.618268965663582</v>
+        <v>8.631335219964058</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>5.784221661556501</v>
+        <v>5.797402670851739</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>7.49836970436828</v>
+        <v>7.511568443323043</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>8.423392448334496</v>
+        <v>8.436797575987327</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>8.810355100348289</v>
+        <v>8.823812394058507</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>4.702726423374187</v>
+        <v>4.716178712094298</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>3.09903985976657</v>
+        <v>3.112595906118173</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>5.715625097368296</v>
+        <v>5.705195461670144</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 65.63</t>
+          <t>X ≈ 65.64</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>149</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-4.842431608800581</v>
+        <v>-4.829909319124958</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.2574041742083182</v>
+        <v>0.2703139837843693</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-4.835451109569554</v>
+        <v>-4.822443978151952</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.6783523393780087</v>
+        <v>-0.6653731969795444</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.1255083247443736</v>
+        <v>0.1386191291193128</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.765232141654586</v>
+        <v>1.778275037948951</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>0.3382165451876773</v>
+        <v>0.3512827994881533</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.5421740860036479</v>
+        <v>0.5553550952988857</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>3.165737958210599</v>
+        <v>3.178936697165362</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>5.000176531571867</v>
+        <v>5.013581659224698</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>2.110859448865028</v>
+        <v>2.124316742575246</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>4.158665425002482</v>
+        <v>4.172117713722592</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>7.765256451641385</v>
+        <v>7.778812497992988</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>8.014977783917672</v>
+        <v>8.00454814821952</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 67.79</t>
+          <t>X ≈ 67.8</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>143</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1.352715525943871</v>
+        <v>1.365237815619494</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>1.839044010881672</v>
+        <v>1.851953820457723</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>4.241378101487996</v>
+        <v>4.254385232905598</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.5234736610094757</v>
+        <v>-0.5104945186110115</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-3.159796973983745</v>
+        <v>-3.146686169608806</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-6.358858532771499</v>
+        <v>-6.345815636477134</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-3.646389452841056</v>
+        <v>-3.63332319854058</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>1.480832742783036</v>
+        <v>1.494013752078274</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.6780692413013725</v>
+        <v>-0.6648705023466093</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>1.9683090701742</v>
+        <v>1.981714197827031</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>1.064255046555957</v>
+        <v>1.077712340266174</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>3.895841001104067</v>
+        <v>3.909293289824177</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>4.174887089459986</v>
+        <v>4.188443135811589</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>5.123909121036938</v>
+        <v>5.113479485338786</v>
       </c>
     </row>
     <row r="27">
@@ -1667,46 +1667,46 @@
         <v>141</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>7.081029764896407</v>
+        <v>7.093552054572029</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>2.632576719308076</v>
+        <v>2.645486528884128</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-2.017611136224723</v>
+        <v>-2.004604004807121</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-1.178138145461197</v>
+        <v>-1.165159003062733</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-1.007339502377334</v>
+        <v>-0.9942286980023951</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.0006777065056482456</v>
+        <v>0.01236518978871715</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>0.6238084343781054</v>
+        <v>0.6368746886785814</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-1.971034538871486</v>
+        <v>-1.957853529576248</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0.09562514941430322</v>
+        <v>0.1088238883690664</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-1.463719893769699</v>
+        <v>-1.450314766116868</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.9592533599312461</v>
+        <v>-0.9457960662210283</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-3.761749635209888</v>
+        <v>-3.748297346489778</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-2.054344671686785</v>
+        <v>-2.040788625335182</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-1.095403481254387</v>
+        <v>-1.105833116952539</v>
       </c>
     </row>
     <row r="28">
@@ -1719,46 +1719,46 @@
         <v>109</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-4.78701630186135</v>
+        <v>-4.774494012185727</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-2.728865144183402</v>
+        <v>-2.715955334607351</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-1.288871465458847</v>
+        <v>-1.275864334041245</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-1.158618332851347</v>
+        <v>-1.145639190452883</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>1.05525403005808</v>
+        <v>1.068364834433019</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.4352647751131968</v>
+        <v>0.4483076714075622</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>3.102824635822621</v>
+        <v>3.115890890123097</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-1.951514726261678</v>
+        <v>-1.93833371696644</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0.7397789655376599</v>
+        <v>0.7529777044924231</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-1.027777412150762</v>
+        <v>-1.014372284497931</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>2.437194034173814</v>
+        <v>2.450651327884032</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>5.223870769500891</v>
+        <v>5.237323058221001</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>5.72104735121659</v>
+        <v>5.734603397568193</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>6.888199876153379</v>
+        <v>6.877770240455227</v>
       </c>
     </row>
     <row r="29">
@@ -1771,46 +1771,46 @@
         <v>95</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>6.453930100842683</v>
+        <v>6.466452390518306</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>8.000251224720508</v>
+        <v>8.013161034296559</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>8.658014097071224</v>
+        <v>8.671021228488826</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>5.630372492836621</v>
+        <v>5.643351635235085</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>11.40774075144871</v>
+        <v>11.42085155582365</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>12.75781426811174</v>
+        <v>12.77085716440611</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>12.67308055083941</v>
+        <v>12.68614680513988</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>12.20589715205796</v>
+        <v>12.2190781613532</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>8.987002529033511</v>
+        <v>9.000201267988274</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>10.24214050190044</v>
+        <v>10.25554562955327</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>8.984755598635431</v>
+        <v>8.998212892345649</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>6.913875598086179</v>
+        <v>6.927327886806289</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>9.651515723983387</v>
+        <v>9.66507177033499</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>9.901237056259674</v>
+        <v>9.890807420561522</v>
       </c>
     </row>
     <row r="30">
@@ -1823,46 +1823,46 @@
         <v>110</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>3.870198043426363</v>
+        <v>3.882720333101986</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>9.531351703189422</v>
+        <v>9.544261512765473</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>8.227392087501912</v>
+        <v>8.240399218919514</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>5.630372492836678</v>
+        <v>5.643351635235142</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>4.182860368673602</v>
+        <v>4.195971173048541</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>4.480302306389284</v>
+        <v>4.493345202683649</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>4.395568589116984</v>
+        <v>4.40863484341746</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>6.655657917608202</v>
+        <v>6.66883892690344</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>4.776476213244145</v>
+        <v>4.789674952198908</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>6.653623755488837</v>
+        <v>6.667028883141668</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>5.539779522080394</v>
+        <v>5.553236815790612</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>6.483253588516668</v>
+        <v>6.496705877236778</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>6.062998977571787</v>
+        <v>6.07655502392339</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>2.676356673484413</v>
+        <v>2.665927037786261</v>
       </c>
     </row>
     <row r="31">
@@ -1875,46 +1875,46 @@
         <v>78</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>6.480920654149003</v>
+        <v>6.493442943824626</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>11.27960345144107</v>
+        <v>11.29251326101712</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>12.16678602689583</v>
+        <v>12.17979315831344</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>11.01498787745204</v>
+        <v>11.0279670198505</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>7.912464098277326</v>
+        <v>7.925574902652265</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>3.08170090778782</v>
+        <v>3.094743804082185</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>0.4328646264130214</v>
+        <v>0.4459308807134974</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>7.657988919939207</v>
+        <v>7.671169929234445</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>6.314937751705628</v>
+        <v>6.328136490660391</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>8.028915130780263</v>
+        <v>8.042320258433094</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>9.106213088513968</v>
+        <v>9.119670382224186</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>12.98675009201328</v>
+        <v>13.00020238073339</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>11.28444419901709</v>
+        <v>11.2980002453687</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>8.970062967190856</v>
+        <v>8.959633331492704</v>
       </c>
     </row>
     <row r="32">
@@ -1927,46 +1927,46 @@
         <v>48</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>10.00656167979002</v>
+        <v>10.01908396946565</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>10.4783214001592</v>
+        <v>10.49123120973525</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>14.25011936022918</v>
+        <v>14.26312649164678</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>22.71370582617008</v>
+        <v>22.72668496856854</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>11.75861794443117</v>
+        <v>11.7717287488061</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>12.05605988214681</v>
+        <v>12.06910277844118</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>16.13799283154125</v>
+        <v>16.15105908584172</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>13.58747609942642</v>
+        <v>13.60065710872166</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>15.60980954657743</v>
+        <v>15.62300828553219</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>18.92635102821616</v>
+        <v>18.93975615586899</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>22.88826437056524</v>
+        <v>22.90172166427546</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>25.00598086124407</v>
+        <v>25.01943314996418</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>22.50239291696571</v>
+        <v>22.51594896331731</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>31.0854475825754</v>
+        <v>31.07501794687725</v>
       </c>
     </row>
     <row r="33">
@@ -1979,98 +1979,98 @@
         <v>55</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>9.324743497971838</v>
+        <v>9.337265787647461</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>2.258624430462127</v>
+        <v>2.271534240038179</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>3.681937542047358</v>
+        <v>3.69494467346496</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.1758270382911959</v>
+        <v>0.1888061806896602</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>1.455587641400847</v>
+        <v>1.468698445775786</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-3.701515875428896</v>
+        <v>-3.688472979134531</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>1.668295861844229</v>
+        <v>1.681362116144705</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>6.655657917608181</v>
+        <v>6.668838926903419</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>8.412839849607721</v>
+        <v>8.426038588562484</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>13.01726011912525</v>
+        <v>13.03066524677809</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>16.44887043117131</v>
+        <v>16.46232772488153</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>16.48325358851669</v>
+        <v>16.4967058772368</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>19.69936261393548</v>
+        <v>19.71291866028709</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>18.13090212802989</v>
+        <v>18.12047249233174</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ 85.03</t>
+          <t>X ≈ 85.02</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>45</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-1.382327209098868</v>
+        <v>-1.369804919423245</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.7716785998409321</v>
+        <v>-0.758768790264881</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>3.277897138006949</v>
+        <v>3.290904269424551</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>12.29703915950338</v>
+        <v>12.31001830190184</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>7.314173499986765</v>
+        <v>7.327284304361704</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>12.05605988214683</v>
+        <v>12.06910277844119</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>16.415770609319</v>
+        <v>16.42883686361948</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>20.39303165498195</v>
+        <v>20.40621266427718</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>15.8875873243552</v>
+        <v>15.90078606330997</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>17.25968436154949</v>
+        <v>17.27308948920232</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>17.05493103723191</v>
+        <v>17.06838833094213</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>19.31153641679957</v>
+        <v>19.32498870551968</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>18.89128180585468</v>
+        <v>18.90483785220628</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>16.91878091590873</v>
+        <v>16.90835128021057</v>
       </c>
     </row>
   </sheetData>
@@ -2121,7 +2121,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that RSI-21 is above threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that RSI-21 is above threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -2217,150 +2217,150 @@
         <v>4074</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.02158320518305601</v>
+        <v>-0.02189963709172815</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.1422340888575917</v>
+        <v>0.141867528873675</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.02999203407834727</v>
+        <v>0.02965035945583594</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.07131744103548243</v>
+        <v>-0.07163367328591619</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.1554764537396522</v>
+        <v>-0.1557755372580516</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.1631674314200922</v>
+        <v>-0.1634629573092496</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.03847775669407838</v>
+        <v>-0.03880450968227933</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.02646114009310452</v>
+        <v>-0.02679387167052738</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.04866846434757122</v>
+        <v>0.04831677617531227</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.07057472210873073</v>
+        <v>0.07021226180327034</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.07586659496826087</v>
+        <v>0.07550140428037366</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.1731587753544375</v>
+        <v>0.1727697544783524</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.1349407814724017</v>
+        <v>0.1345583702703408</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.2128408079067654</v>
+        <v>0.2024111722086133</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; 25.79</t>
+          <t>X &gt; 25.8</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>4028</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.04172955349377361</v>
+        <v>-0.04219357448087635</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.1184213093325823</v>
+        <v>0.1179028293488216</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.04001939100966467</v>
+        <v>-0.0405024407287442</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.004598019478564197</v>
+        <v>0.004104856246044619</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.1237155541640931</v>
+        <v>-0.1241820318630289</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.08543941531576849</v>
+        <v>-0.08591292144311069</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.0417626728110676</v>
+        <v>0.04125662282822162</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.1587363326191493</v>
+        <v>0.1581967912613109</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.1610915978594747</v>
+        <v>0.1605506654213755</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.1934148157564906</v>
+        <v>0.192857892841694</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.1872219282718675</v>
+        <v>0.2006792219820852</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.2356233637266314</v>
+        <v>0.2350573743374085</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.2374144330200636</v>
+        <v>0.2509704793716665</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.2885260334194868</v>
+        <v>0.2780963977213347</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; 27.94</t>
+          <t>X &gt; 27.95</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>3966</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.06576536423512636</v>
+        <v>-0.06642910900517052</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.1727938041181716</v>
+        <v>0.1720488197980501</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.007054060359799053</v>
+        <v>-0.007759265776464019</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.1117420799464526</v>
+        <v>0.1110083178427459</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.01003814555456017</v>
+        <v>-0.01074859258361727</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.1249095882761395</v>
+        <v>0.1241686728422735</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.2807239980819105</v>
+        <v>0.2799423771934997</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.3818309381360621</v>
+        <v>0.3810174009866856</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.2844167224449947</v>
+        <v>0.2836265651020753</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.2803601053719831</v>
+        <v>0.2795595337363963</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.4286072853408385</v>
+        <v>0.4420645790510562</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.3369188340125433</v>
+        <v>0.3503711227326534</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.3200933708235709</v>
+        <v>0.3336494171751738</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.3933144509566375</v>
+        <v>0.3828848152584854</v>
       </c>
     </row>
     <row r="9">
@@ -2370,101 +2370,101 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3890</v>
+        <v>3889</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.06111880430863437</v>
+        <v>0.04796715303432109</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.2863594073496571</v>
+        <v>0.273588682770594</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.01747632433286128</v>
+        <v>-0.004469192915259157</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.178162831993923</v>
+        <v>0.1911419743923872</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.03926559285060449</v>
+        <v>0.05237639722554377</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.1311048577315148</v>
+        <v>0.158220173471193</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.2660990868968298</v>
+        <v>0.2791653411973058</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.3387614464700945</v>
+        <v>0.3662138071016656</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.4062962646579678</v>
+        <v>0.4337994057858907</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.4302070693472686</v>
+        <v>0.4581413448635914</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.508230094644091</v>
+        <v>0.5362892480587789</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.4654924293674085</v>
+        <v>0.4935267472899056</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.4565488724070832</v>
+        <v>0.4847927106388781</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.3977869141949313</v>
+        <v>0.4019657483686387</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; 32.25</t>
+          <t>X &gt; 32.26</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>3804</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.009864075794730809</v>
+        <v>-0.01113147982494667</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.2588156167731839</v>
+        <v>0.2574379552454502</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.07425185234274778</v>
+        <v>0.08725898376034991</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.2833693382625526</v>
+        <v>0.2963484806610168</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.08669365421035735</v>
+        <v>0.09980445858529663</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.2001187675306468</v>
+        <v>0.2131616638250122</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.4045543457368055</v>
+        <v>0.4176206000372815</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.4631333023706574</v>
+        <v>0.4763143116658952</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.5861502405837271</v>
+        <v>0.5993489795384903</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.6561091775326702</v>
+        <v>0.6695143051855013</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.5039320887566276</v>
+        <v>0.5173893824668454</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.5383152461020586</v>
+        <v>0.5517675348221687</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.5123824017186678</v>
+        <v>0.5259384480702707</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.4466463207457494</v>
+        <v>0.4362166850475973</v>
       </c>
     </row>
     <row r="11">
@@ -2477,46 +2477,46 @@
         <v>3692</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.06545688693868357</v>
+        <v>0.06375099707799592</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.2828537222970553</v>
+        <v>0.281036246290796</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.1588409203591823</v>
+        <v>0.1718480517767844</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.3432652338984354</v>
+        <v>0.3562443762968996</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.1840422853484753</v>
+        <v>0.1971530897234146</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.3731418612006436</v>
+        <v>0.386184757495009</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.5592640485870817</v>
+        <v>0.5723303028875577</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.6608780495889022</v>
+        <v>0.67405905888414</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.7082205252700859</v>
+        <v>0.7214192642248491</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.8602621874794352</v>
+        <v>0.8736673151322663</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.7096800440935951</v>
+        <v>0.7231373378038128</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.744063201439026</v>
+        <v>0.7575154901591361</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.6488356760845875</v>
+        <v>0.6623917224361904</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.4381019704410534</v>
+        <v>0.4276723347429012</v>
       </c>
     </row>
     <row r="12">
@@ -2529,98 +2529,98 @@
         <v>3575</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.3736945469228985</v>
+        <v>0.3714329627542341</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.3285545003922081</v>
+        <v>0.3414643099682593</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.07354593365575113</v>
+        <v>0.08655306507335325</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.2597431222073112</v>
+        <v>0.2727222646057754</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.001042186855414684</v>
+        <v>0.01415299123035396</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.270512096599056</v>
+        <v>0.2835549928934213</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.4095546031029897</v>
+        <v>0.4226208574034658</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.5577558197061094</v>
+        <v>0.5709368290013472</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.7485041852720613</v>
+        <v>0.7617029242268245</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.9333440352091742</v>
+        <v>0.9467491628620053</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.6726466549475347</v>
+        <v>0.6861039486577525</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.7070298122929657</v>
+        <v>0.7204821010130757</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.6224395370123972</v>
+        <v>0.6359955833640001</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.4525804497082646</v>
+        <v>0.4421508140101125</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; 38.71</t>
+          <t>X &gt; 38.72</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>3403</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.4304523644800042</v>
+        <v>0.4274270952000734</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.5526430771108153</v>
+        <v>0.5655528866868664</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.1577743705142254</v>
+        <v>0.1707815019318275</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.2880275031217252</v>
+        <v>0.3010066455201894</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.01530702373416659</v>
+        <v>-0.002196219359227314</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.3409065860355653</v>
+        <v>0.3539494823299307</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.4912595569795641</v>
+        <v>0.5043258112800402</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.6411787147657932</v>
+        <v>0.654359724061031</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.7564938447456981</v>
+        <v>0.7696925837004613</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>1.08180210079918</v>
+        <v>1.095207228452011</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.7888912684004907</v>
+        <v>0.8023485621107085</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.9408177698540641</v>
+        <v>0.9542700585741741</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.9319648632876465</v>
+        <v>0.9455209096392494</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.9759853433746954</v>
+        <v>0.9655557076765433</v>
       </c>
     </row>
     <row r="14">
@@ -2630,101 +2630,101 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3236</v>
+        <v>3234</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.1641636575403354</v>
+        <v>0.1311396108876011</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.715754445070516</v>
+        <v>0.731645557292353</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.1426494902034605</v>
+        <v>-0.1269477198559983</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.0185059909825398</v>
+        <v>0.034198883225244</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.4272081783541566</v>
+        <v>-0.4113262913917879</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.1174525479894371</v>
+        <v>0.133419414186406</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.1563282250311318</v>
+        <v>0.1723948928917949</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.3998988435549506</v>
+        <v>0.4165198174414755</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.586117746000582</v>
+        <v>0.6029093368618064</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>1.002988852690827</v>
+        <v>1.020770379740355</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.7364308312162606</v>
+        <v>0.7542263024943878</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>1.079837474346611</v>
+        <v>1.097819049778593</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>1.092215743500589</v>
+        <v>1.079647169872729</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>1.00201124141347</v>
+        <v>0.9961682251703792</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; 43.02</t>
+          <t>X &gt; 43.03</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3042</v>
+        <v>3041</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.1923206344769071</v>
+        <v>-0.1954836069894625</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.6287158774766581</v>
+        <v>0.6267403624261547</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.1277570368779948</v>
+        <v>-0.1297541397244828</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.09612323365904984</v>
+        <v>-0.0981807554258225</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.6016713389350272</v>
+        <v>-0.6035863887582806</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.008371413053687604</v>
+        <v>-0.01025708125407476</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.3342452970244594</v>
+        <v>0.332523516401821</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.6231434235552555</v>
+        <v>0.6217850271695085</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.6607628667615089</v>
+        <v>0.6594546299364339</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>1.059815853988681</v>
+        <v>1.05912478460953</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.8550625296711019</v>
+        <v>0.8544236263493374</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>1.316796114366959</v>
+        <v>1.316292735626739</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>1.323891930772483</v>
+        <v>1.323632839235387</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>1.409247714067838</v>
+        <v>1.384948890645738</v>
       </c>
     </row>
     <row r="16">
@@ -2737,46 +2737,46 @@
         <v>2853</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.4780159577844643</v>
+        <v>-0.4654936681088415</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.6794255011054773</v>
+        <v>0.6923353106815284</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.136053089823406</v>
+        <v>-0.1230459584058039</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.2395558086445959</v>
+        <v>0.2525349510430601</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.3689670538162844</v>
+        <v>-0.3558562494413451</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.3140339445373002</v>
+        <v>0.3270768408316655</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.7200117589860184</v>
+        <v>0.7330780132864945</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1.199200599952157</v>
+        <v>1.212381609247394</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.9979974189924263</v>
+        <v>1.01119615794719</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>1.479803534350054</v>
+        <v>1.493208662002885</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>1.485355152198615</v>
+        <v>1.498812445908833</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>1.519738309544046</v>
+        <v>1.533190598264156</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>1.730398525097563</v>
+        <v>1.743954571449166</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>1.839916562596436</v>
+        <v>1.829486926898284</v>
       </c>
     </row>
     <row r="17">
@@ -2789,98 +2789,98 @@
         <v>2618</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.4477381503782638</v>
+        <v>0.4602604400538866</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.6696251944040768</v>
+        <v>0.6825350039801279</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.08377100270435278</v>
+        <v>0.09677813412195491</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.4432067174356078</v>
+        <v>0.456185859834072</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.21036227852845</v>
+        <v>0.2234730829033893</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.5841984102853672</v>
+        <v>0.5972413065797326</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>1.110618245343112</v>
+        <v>1.123684499643588</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1.636559369097888</v>
+        <v>1.649740378393126</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>1.575559482915587</v>
+        <v>1.58875822187035</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>1.947741402547713</v>
+        <v>1.961146530200544</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>1.933973563333268</v>
+        <v>1.947430857043486</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>1.815568332596193</v>
+        <v>1.829020621316303</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>1.662693400795675</v>
+        <v>1.676249447147278</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>1.6832321509482</v>
+        <v>1.672802515250048</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; 49.48</t>
+          <t>X &gt; 49.49</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>2399</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1.153914743566595</v>
+        <v>1.166437033242218</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>1.168018496171328</v>
+        <v>1.180928305747379</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.7731497895747381</v>
+        <v>0.7861569209923402</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>1.361927307342725</v>
+        <v>1.374906449741189</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.9902422323289102</v>
+        <v>1.003353036703849</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1.579472415146704</v>
+        <v>1.592515311441069</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>1.911579048020307</v>
+        <v>1.924645302320783</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>2.23639231451601</v>
+        <v>2.249573323811248</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>2.342128568392063</v>
+        <v>2.355327307346826</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>2.575788293743464</v>
+        <v>2.589193421396295</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>2.412719004440476</v>
+        <v>2.426176298150693</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>2.196997951698371</v>
+        <v>2.210450240418481</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1.943479480811824</v>
+        <v>1.957035527163427</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>2.026464673029757</v>
+        <v>2.016035037331605</v>
       </c>
     </row>
     <row r="19">
@@ -2893,46 +2893,46 @@
         <v>2204</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>1.453930100842655</v>
+        <v>1.466452390518278</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>1.657238520546272</v>
+        <v>1.670148330122323</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1.670718271299954</v>
+        <v>1.683725402717556</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>1.937087556357554</v>
+        <v>1.950066698756018</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1.670898646185556</v>
+        <v>1.684009450560495</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.968340583901217</v>
+        <v>1.981383480195582</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>2.700303781329481</v>
+        <v>2.713370035629957</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>2.777584992348352</v>
+        <v>2.79076600164359</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>2.852701258616143</v>
+        <v>2.865899997570907</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>3.318365547272421</v>
+        <v>3.331770674925252</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>3.022868121321451</v>
+        <v>3.036325415031669</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>2.694274872133306</v>
+        <v>2.707727160853416</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>2.546252566088576</v>
+        <v>2.559808612440179</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>2.659857745914785</v>
+        <v>2.649428110216633</v>
       </c>
     </row>
     <row r="20">
@@ -2945,98 +2945,98 @@
         <v>1967</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1.904121415428051</v>
+        <v>1.916643705103674</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>2.326101437440919</v>
+        <v>2.33901124701697</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>2.744654184835177</v>
+        <v>2.757661316252779</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>2.722390794819397</v>
+        <v>2.735369937217861</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>2.082291897998367</v>
+        <v>2.095402702373306</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>2.328894994839608</v>
+        <v>2.341937891133973</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>3.413454617679172</v>
+        <v>3.426520871979648</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>3.251304264144231</v>
+        <v>3.264485273439469</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>3.291982059710783</v>
+        <v>3.305180798665546</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>3.967022100915706</v>
+        <v>3.980427228568537</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>3.762268776598127</v>
+        <v>3.775726070308345</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>3.694974252194704</v>
+        <v>3.708426540914814</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>3.630591527370797</v>
+        <v>3.6441475737224</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>3.82947401877265</v>
+        <v>3.819044383074498</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 55.94</t>
+          <t>X &gt; 55.95</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>1760</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1.881561679790018</v>
+        <v>1.89408396946564</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>2.144988066825768</v>
+        <v>2.157897876401819</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>2.488755723865545</v>
+        <v>2.501762855283147</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>2.903099765563951</v>
+        <v>2.916078907962415</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>2.478314914128141</v>
+        <v>2.491425718503081</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>2.662120488207442</v>
+        <v>2.675163384501808</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>3.316023134571523</v>
+        <v>3.329089388871999</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>3.701112463062749</v>
+        <v>3.714293472357987</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>3.640112576880448</v>
+        <v>3.653311315835211</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>4.039987391852527</v>
+        <v>4.053392519505358</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>3.892052249353128</v>
+        <v>3.905509543063346</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>3.812799043062199</v>
+        <v>3.826251331782309</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>4.01754443211729</v>
+        <v>4.031100478468893</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>4.096811218939031</v>
+        <v>4.086381583240879</v>
       </c>
     </row>
     <row r="22">
@@ -3049,46 +3049,46 @@
         <v>1555</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>2.23324978268392</v>
+        <v>2.245772072359543</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>2.229393211520303</v>
+        <v>2.242303021096355</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>2.541920003315994</v>
+        <v>2.554927134733596</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>2.993716544283622</v>
+        <v>3.006695686682086</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>2.583912692555501</v>
+        <v>2.59702349693044</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>2.624119903583065</v>
+        <v>2.63716279987743</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>3.632633774735218</v>
+        <v>3.645700029035694</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>3.937154556018029</v>
+        <v>3.950335565313267</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>4.262006759867887</v>
+        <v>4.27520549882265</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>5.0195986166406</v>
+        <v>5.033003744293431</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>4.493301883962893</v>
+        <v>4.506759177673111</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>4.656302404652379</v>
+        <v>4.669754693372489</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>4.879134610427727</v>
+        <v>4.89269065677933</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>5.193164624376045</v>
+        <v>5.182734988677893</v>
       </c>
     </row>
     <row r="23">
@@ -3101,46 +3101,46 @@
         <v>1383</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>2.242642663159508</v>
+        <v>2.255164952835131</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>2.583346707462063</v>
+        <v>2.596256517038114</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>2.839237219954406</v>
+        <v>2.852244351372008</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>3.114103512359456</v>
+        <v>3.12708265475792</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>3.081828356578676</v>
+        <v>3.094939160953615</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>2.583897915407867</v>
+        <v>2.596940811702233</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>4.017602376009769</v>
+        <v>4.030668630310245</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>4.490404515912282</v>
+        <v>4.503585525207519</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>4.863244109122611</v>
+        <v>4.876442848077374</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>5.748476841665187</v>
+        <v>5.761881969318019</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>5.109884037954977</v>
+        <v>5.123341331665195</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>5.361186934996731</v>
+        <v>5.374639223716841</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>6.025531022533379</v>
+        <v>6.039087068884982</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>6.419865514607217</v>
+        <v>6.409435878909065</v>
       </c>
     </row>
     <row r="24">
@@ -3153,46 +3153,46 @@
         <v>1226</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>2.482091859235375</v>
+        <v>2.494614148910998</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>2.991236027674056</v>
+        <v>3.004145837250107</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>3.330461937716947</v>
+        <v>3.343469069134549</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>4.113243618448422</v>
+        <v>4.126222760846886</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>3.901086677438251</v>
+        <v>3.91419748181319</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>3.790698272576421</v>
+        <v>3.803741168870786</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>4.603191308974608</v>
+        <v>4.616257563275084</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>4.951668595348082</v>
+        <v>4.964849604643319</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>5.216932983227771</v>
+        <v>5.230131722182534</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>6.24282737405629</v>
+        <v>6.256232501709121</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>6.11964011825421</v>
+        <v>6.133097411964428</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>6.643419686692631</v>
+        <v>6.656871975412741</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>7.283523966449188</v>
+        <v>7.297080012800791</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>7.696377435756474</v>
+        <v>7.685947800058322</v>
       </c>
     </row>
     <row r="25">
@@ -3205,98 +3205,98 @@
         <v>1057</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>2.568056476384157</v>
+        <v>2.58057876605978</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>3.416274727185275</v>
+        <v>3.429184536761326</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>3.21062077933987</v>
+        <v>3.223627910757472</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>3.719303429449738</v>
+        <v>3.732282571848202</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>3.370096973128746</v>
+        <v>3.383207777503685</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>2.910679875839676</v>
+        <v>2.923722772134042</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>3.961234711074489</v>
+        <v>3.974300965374965</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>4.818554623551279</v>
+        <v>4.831735632846517</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>4.852162116744566</v>
+        <v>4.865360855699329</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>5.89418451922846</v>
+        <v>5.907589646881291</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>5.689431194910881</v>
+        <v>5.702888488621099</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>6.953710284138999</v>
+        <v>6.96716257285911</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>7.952566363827962</v>
+        <v>7.966122410179565</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>8.013072937353073</v>
+        <v>8.002643301654921</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 66.71</t>
+          <t>X &gt; 66.72</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>908</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>3.784094719437604</v>
+        <v>3.796617009113227</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>3.934635643918277</v>
+        <v>3.947545453494328</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>4.53095636463447</v>
+        <v>4.543963496052072</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>4.440945180061348</v>
+        <v>4.453924322459812</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>3.902523964989179</v>
+        <v>3.915634769364118</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>3.09864431680176</v>
+        <v>3.111687213096126</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>4.555760819793797</v>
+        <v>4.568827074094273</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>5.520295482686301</v>
+        <v>5.533476491981538</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>5.128899120733074</v>
+        <v>5.142097859687837</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>6.040888473150083</v>
+        <v>6.054293600802914</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>6.276663783193733</v>
+        <v>6.290121076903951</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>7.412368526442243</v>
+        <v>7.425820815162353</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>7.983303342810125</v>
+        <v>7.996859389161727</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>8.01276035790579</v>
+        <v>8.002330722207638</v>
       </c>
     </row>
     <row r="27">
@@ -3309,46 +3309,46 @@
         <v>765</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>4.238587823580872</v>
+        <v>4.251110113256495</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>4.326360615845381</v>
+        <v>4.339270425421432</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>4.585086680490619</v>
+        <v>4.598093811908221</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>5.368934584339947</v>
+        <v>5.381913726738411</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>5.222670232012874</v>
+        <v>5.235781036387813</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>4.866517398486707</v>
+        <v>4.879560294781072</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>6.088973223698083</v>
+        <v>6.102039477998559</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>6.275384596158418</v>
+        <v>6.288565605453655</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>6.214384709976116</v>
+        <v>6.227583448930879</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>6.80216802168021</v>
+        <v>6.815573149333041</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>7.251009468604458</v>
+        <v>7.264466762314676</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>8.06970635144009</v>
+        <v>8.0831586401602</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>8.695203374482112</v>
+        <v>8.708759420833715</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>8.552767844013303</v>
+        <v>8.542338208315151</v>
       </c>
     </row>
     <row r="28">
@@ -3361,46 +3361,46 @@
         <v>624</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>3.596305269533616</v>
+        <v>3.608827559209239</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>4.709090630928337</v>
+        <v>4.722000440504388</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>6.077042437152251</v>
+        <v>6.090049568569853</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>6.8483212107854</v>
+        <v>6.861300353183864</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>6.630412816226048</v>
+        <v>6.643523620600988</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>5.966316292403242</v>
+        <v>5.979359188697607</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>7.323890267438664</v>
+        <v>7.33695652173914</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>8.138758150708441</v>
+        <v>8.151939160003678</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>7.596989033756905</v>
+        <v>7.610187772711669</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>8.669940771805912</v>
+        <v>8.683345899458743</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>9.106213088513968</v>
+        <v>9.119670382224186</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>10.7431603484235</v>
+        <v>10.75661263714361</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>11.12418778876066</v>
+        <v>11.13774383511226</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>10.7328834800113</v>
+        <v>10.72245384431314</v>
       </c>
     </row>
     <row r="29">
@@ -3413,46 +3413,46 @@
         <v>515</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>5.370639349692937</v>
+        <v>5.383161639368559</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>6.283337581388878</v>
+        <v>6.296247390964929</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>7.636041690326259</v>
+        <v>7.649048821743861</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>8.542993852059972</v>
+        <v>8.555972994458436</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>7.810397879706258</v>
+        <v>7.823508684081197</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>7.136966031014147</v>
+        <v>7.150008927308512</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>8.217280857431184</v>
+        <v>8.23034711173166</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>10.27436930330989</v>
+        <v>10.28755031260513</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>9.048320873438264</v>
+        <v>9.061519612393028</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>10.72246753307053</v>
+        <v>10.73587266072336</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>10.51771420875295</v>
+        <v>10.53117150246317</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>11.91132066706926</v>
+        <v>11.92477295578937</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>12.26776508525057</v>
+        <v>12.28132113160217</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>11.54661263111909</v>
+        <v>11.53618299542094</v>
       </c>
     </row>
     <row r="30">
@@ -3465,46 +3465,46 @@
         <v>420</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>5.125609298837638</v>
+        <v>5.138131588513261</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>5.894988066825768</v>
+        <v>5.907897876401819</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>7.404881264991083</v>
+        <v>7.417888396408685</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>9.201801064265247</v>
+        <v>9.214780206663711</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>6.996713182526413</v>
+        <v>7.009823986901353</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>5.865583691670643</v>
+        <v>5.878626587965009</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>7.209421402969795</v>
+        <v>7.222487657270271</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>9.837476099426389</v>
+        <v>9.850657108721627</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>9.06219049895838</v>
+        <v>9.075389237913143</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>10.83111293297806</v>
+        <v>10.84451806063089</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>10.86445484675572</v>
+        <v>10.87791214046594</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>13.04169514695829</v>
+        <v>13.0551474356784</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>12.85953577410863</v>
+        <v>12.87309182046023</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>11.91878091590873</v>
+        <v>11.90835128021057</v>
       </c>
     </row>
     <row r="31">
@@ -3517,46 +3517,46 @@
         <v>310</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>5.571077808822288</v>
+        <v>5.583600098497911</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>4.6046654861806</v>
+        <v>4.617575295756652</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>7.113022586035626</v>
+        <v>7.126029717453228</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>10.46908217025604</v>
+        <v>10.4820613126545</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>7.995177084216124</v>
+        <v>8.008287888591063</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>6.357135150964034</v>
+        <v>6.370178047258399</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>8.207885304659506</v>
+        <v>8.220951558959982</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>10.9665083574909</v>
+        <v>10.97968936678614</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>10.58292782614732</v>
+        <v>10.59612656510208</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>12.31344780240971</v>
+        <v>12.32685293006254</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>12.75385576841471</v>
+        <v>12.76731306212493</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>15.36888408705047</v>
+        <v>15.38233637577058</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>15.27121012126685</v>
+        <v>15.28476616761846</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>15.19835080838186</v>
+        <v>15.18792117268371</v>
       </c>
     </row>
     <row r="32">
@@ -3569,46 +3569,46 @@
         <v>232</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>5.265182369445199</v>
+        <v>5.277704659120822</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>2.360505308205084</v>
+        <v>2.373415117781136</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>5.413912463677455</v>
+        <v>5.426919595095058</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>10.28554490662979</v>
+        <v>10.29852404902825</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>8.022985760523127</v>
+        <v>8.036096564898067</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>7.45835873272155</v>
+        <v>7.471401629015915</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>10.82190087751824</v>
+        <v>10.83496713181871</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>12.07885540977122</v>
+        <v>12.09203641906645</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>12.01785552358891</v>
+        <v>12.03105426254368</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>13.75393723511272</v>
+        <v>13.76734236276555</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>13.98021839355376</v>
+        <v>13.99367568726397</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>16.16977396469228</v>
+        <v>16.18322625341239</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>16.61158831926462</v>
+        <v>16.62514436561622</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>17.29234413429953</v>
+        <v>17.28191449860137</v>
       </c>
     </row>
     <row r="33">
@@ -3621,98 +3621,98 @@
         <v>184</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>4.028300810224806</v>
+        <v>4.040823099900429</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.2428141537822839</v>
+        <v>0.255723963358335</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>3.108815012403092</v>
+        <v>3.121822143820694</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>7.043415971097545</v>
+        <v>7.056395113496009</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>7.048473016894938</v>
+        <v>7.061583821269878</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>6.258958432871481</v>
+        <v>6.272001329165846</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>9.435094280816578</v>
+        <v>9.448160535117054</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>11.68530218638291</v>
+        <v>11.69848319567814</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>11.08082403933104</v>
+        <v>11.0940227782858</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>12.40461189778138</v>
+        <v>12.41801702543421</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>11.65638031259424</v>
+        <v>11.66983760630445</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>13.86467651341792</v>
+        <v>13.87812880213803</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>15.07485668508172</v>
+        <v>15.08841273143332</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>13.6941432347493</v>
+        <v>13.68371359905115</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; 83.95</t>
+          <t>X &gt; 83.94</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>129</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>1.77012757126289</v>
+        <v>1.782649860938513</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.6166398401509809</v>
+        <v>-0.6037300305749298</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>2.864460445500498</v>
+        <v>2.8774675769181</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>9.971457764154515</v>
+        <v>9.984436906552979</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>9.433036549082345</v>
+        <v>9.446147353457285</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>10.50567228524761</v>
+        <v>10.51871518154198</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>12.74651996332417</v>
+        <v>12.75958621762464</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>13.8297241614419</v>
+        <v>13.84290517073713</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>12.21833667836037</v>
+        <v>12.23153541731513</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>12.14340529178205</v>
+        <v>12.15681041943488</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>9.613070572115632</v>
+        <v>9.62652786582585</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>12.74822892325952</v>
+        <v>12.76168121197963</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>13.10316811076422</v>
+        <v>13.11672415711583</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>11.80250184614128</v>
+        <v>11.79207221044313</v>
       </c>
     </row>
     <row r="35">
@@ -3725,46 +3725,46 @@
         <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>3.458942632170981</v>
+        <v>3.471464921846604</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.5335833617456629</v>
+        <v>-0.5206735521696118</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>2.642976503086317</v>
+        <v>2.655983634503919</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>8.725610588074773</v>
+        <v>8.738589730473237</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>10.56814175395499</v>
+        <v>10.58125255832993</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>9.675107501194461</v>
+        <v>9.688150397488826</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>10.78084997439837</v>
+        <v>10.79391622869885</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>10.31366657561687</v>
+        <v>10.32684758491211</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>10.25266668943457</v>
+        <v>10.26586542838933</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>9.402541504406642</v>
+        <v>9.415946632059473</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>5.626359608660486</v>
+        <v>5.639816902370704</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>9.232171337434494</v>
+        <v>9.245623626154604</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>10.00239291696577</v>
+        <v>10.01594896331737</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>9.06163805876588</v>
+        <v>9.051208423067727</v>
       </c>
     </row>
   </sheetData>
@@ -3815,7 +3815,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that RSI-21 is below threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that RSI-21 is below threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -3908,153 +3908,153 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>1.077990251218594</v>
+        <v>1.090512540894217</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-4.105011933174232</v>
+        <v>-4.092102123598181</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-2.118928258818435</v>
+        <v>-2.105921127400833</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>3.963705826170013</v>
+        <v>3.976684968568478</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>8.187189373002603</v>
+        <v>8.200300177377542</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>9.675107501194461</v>
+        <v>9.688150397488826</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>4.828469022017416</v>
+        <v>4.841535276317892</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>3.170809432759725</v>
+        <v>3.183990442054963</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>1.919333356101227</v>
+        <v>1.93253209505599</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>1.069208171073299</v>
+        <v>1.08261329872613</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.3260213437204627</v>
+        <v>-0.3125640500102449</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-5.053542948279798</v>
+        <v>-5.040090659559688</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-3.09284517827232</v>
+        <v>-3.079289131920717</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-7.016962055978823</v>
+        <v>-6.424982053122754</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; 25.79</t>
+          <t>X &lt; 25.8</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>1.294440467668807</v>
+        <v>1.306962757344429</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-1.832284660446959</v>
+        <v>-1.819374850870908</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.8031496632594752</v>
+        <v>0.8161567946770774</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.1758270382912173</v>
+        <v>0.1888061806896815</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>4.182860368673602</v>
+        <v>4.195971173048541</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>3.722726548813505</v>
+        <v>3.73576944510787</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.6076898012381875</v>
+        <v>0.6207560555386635</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-3.647372385422095</v>
+        <v>-3.634191376126857</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-2.193220756452881</v>
+        <v>-2.180022017498118</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-3.043345941480808</v>
+        <v>-3.029940813827977</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-3.606646570910577</v>
+        <v>-3.992217729663928</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-5.09898097081706</v>
+        <v>-5.08552868209695</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-5.125812211239356</v>
+        <v>-5.505679535410358</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-6.802149316649405</v>
+        <v>-6.424982053122754</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; 27.94</t>
+          <t>X &lt; 27.95</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1.352715525943871</v>
+        <v>1.365237815619494</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-2.31014013830243</v>
+        <v>-2.297230328726378</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.1409062807964645</v>
+        <v>-0.1278991493788624</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-2.061935199471009</v>
+        <v>-2.048956057072544</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.476566662379895</v>
+        <v>0.4896774667548343</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-1.790093964007006</v>
+        <v>-1.777051067712641</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-4.438930245381854</v>
+        <v>-4.425863991081378</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-6.957395695445406</v>
+        <v>-6.944214686150168</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-3.941472504704635</v>
+        <v>-3.928273765749871</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-3.765956664091526</v>
+        <v>-3.752551536438695</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-7.309330131152969</v>
+        <v>-7.546996284442486</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-5.466817066217125</v>
+        <v>-5.715102932510106</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-5.101773749700889</v>
+        <v>-5.355380915784515</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-6.67633252213664</v>
+        <v>-6.424982053122754</v>
       </c>
     </row>
     <row r="9">
@@ -4064,101 +4064,101 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.8570746838463421</v>
+        <v>-0.6693218276358053</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-3.195921024083326</v>
+        <v>-3.005145601859049</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.04557390568371744</v>
+        <v>-0.1390474213967039</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-2.369627507163322</v>
+        <v>-2.545054161866311</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.3625941767809522</v>
+        <v>-0.5471118309040364</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-1.325935251673116</v>
+        <v>-1.699013163587786</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-2.870522983543928</v>
+        <v>-3.045910611128001</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-4.246772984822698</v>
+        <v>-4.603888345823826</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-4.488229669108854</v>
+        <v>-4.845361544151508</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-4.782136056654686</v>
+        <v>-5.144492928380096</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-6.278402296101419</v>
+        <v>-6.63259206121473</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-5.686398320912126</v>
+        <v>-6.046065005017432</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-5.544870764626268</v>
+        <v>-5.909976962608546</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-4.729159158997632</v>
+        <v>-4.752119599591154</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; 32.25</t>
+          <t>X &lt; 32.26</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.1093014058174191</v>
+        <v>0.1218236954930418</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-2.050217412626289</v>
+        <v>-2.037307603050238</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.9284520683422528</v>
+        <v>-1.062215974106643</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-2.854475992011807</v>
+        <v>-2.983021991138493</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.7644023133957205</v>
+        <v>-0.9004475597338271</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-1.702019526902099</v>
+        <v>-1.83513294899894</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-3.584229390681003</v>
+        <v>-3.712745161619054</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-4.466145070490043</v>
+        <v>-4.593787335722816</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-5.223523786755912</v>
+        <v>-5.349600813817858</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-5.933592949374876</v>
+        <v>-6.060243844131008</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-4.593009037674449</v>
+        <v>-4.724328755892607</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-4.976413504953172</v>
+        <v>-5.1069713444179</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-4.686872619757388</v>
+        <v>-4.819731787856334</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-4.006620406093155</v>
+        <v>-3.882609171766816</v>
       </c>
     </row>
     <row r="11">
@@ -4168,49 +4168,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.5018240644447829</v>
+        <v>-0.4893017747691601</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-1.694110465668992</v>
+        <v>-1.68120065609294</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-1.348620135569142</v>
+        <v>-1.44704122323791</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-2.580153822952795</v>
+        <v>-2.675976095857287</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-1.321550831940129</v>
+        <v>-1.421253707334238</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-2.602150124900383</v>
+        <v>-2.698829711010276</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-3.847882874673466</v>
+        <v>-3.942316530789732</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-4.844052562993994</v>
+        <v>-4.937478484498712</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-4.797991871862294</v>
+        <v>-4.891853710221532</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-5.967039163681498</v>
+        <v>-6.060243844131008</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-4.996351014050141</v>
+        <v>-5.092237113265398</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-5.280421708349138</v>
+        <v>-5.375865995335026</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-4.518351002919772</v>
+        <v>-4.616456461379258</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-2.866165320650403</v>
+        <v>-2.776913383594859</v>
       </c>
     </row>
     <row r="12">
@@ -4220,101 +4220,101 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-2.241337479873842</v>
+        <v>-2.228815190198219</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-1.579759407921699</v>
+        <v>-1.655127333682209</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.5369801338686315</v>
+        <v>-0.6148196362993517</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-1.498005885541701</v>
+        <v>-1.574186307429279</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.08349104087786685</v>
+        <v>0.003710730788100136</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-1.39026780146898</v>
+        <v>-1.467276240171323</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-2.063761554423692</v>
+        <v>-2.139901366135696</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-3.121707574042993</v>
+        <v>-3.196881091617932</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-3.945840652173295</v>
+        <v>-4.019848857324959</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-5.049758186800901</v>
+        <v>-5.123276212103754</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-3.628829646528764</v>
+        <v>-3.705218039933861</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-3.846758864783389</v>
+        <v>-3.922874542343564</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-3.319505310592831</v>
+        <v>-3.397293045815047</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-2.290841077218417</v>
+        <v>-2.222580680910063</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; 38.71</t>
+          <t>X &lt; 38.72</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-1.906736886050908</v>
+        <v>-1.894214596375285</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-2.146787390093287</v>
+        <v>-2.201619724641212</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.7743904436923899</v>
+        <v>-0.831521027935473</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-1.228266250618816</v>
+        <v>-1.284752939928254</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.1378228373975361</v>
+        <v>0.07888407166824152</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-1.329766889506708</v>
+        <v>-1.386554713913533</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-1.870110541213919</v>
+        <v>-1.926368735680612</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-2.662523900573611</v>
+        <v>-2.718331064734357</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-2.917858437612296</v>
+        <v>-2.973482942537991</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-4.358609393947432</v>
+        <v>-4.413340023314142</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-3.174042983023476</v>
+        <v>-3.23064421083447</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-3.863066757803601</v>
+        <v>-3.918809914765077</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-3.816591630495594</v>
+        <v>-3.872939925571508</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-4.027284512915323</v>
+        <v>-3.974650927294945</v>
       </c>
     </row>
     <row r="14">
@@ -4324,101 +4324,101 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>921</v>
+        <v>924</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.5662434593962686</v>
+        <v>-0.4510015006198174</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-2.22934205107348</v>
+        <v>-2.275862807358862</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.4357416778257459</v>
+        <v>0.3794366520745882</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.01946639008491502</v>
+        <v>-0.07399311851218471</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>1.543564180990323</v>
+        <v>1.482339681281999</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.251080412076341</v>
+        <v>-0.3057183946632378</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.2772370535162452</v>
+        <v>-0.3321131304132265</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-1.225091322364335</v>
+        <v>-1.278375149342892</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-1.659808883948131</v>
+        <v>-1.711939687198353</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-3.100675998810864</v>
+        <v>-3.150761085510325</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-2.274073291772417</v>
+        <v>-2.327512424181926</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-3.48128891123703</v>
+        <v>-3.530782832757261</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-3.518937524104359</v>
+        <v>-3.461528514160094</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-3.21151224370039</v>
+        <v>-3.178228806369511</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; 43.02</t>
+          <t>X &lt; 43.03</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1115</v>
+        <v>1117</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.5207460769531451</v>
+        <v>0.5279335269877663</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-1.48744316653714</v>
+        <v>-1.479170325546804</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.2958564827869097</v>
+        <v>0.3003605341999673</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.2970391595033419</v>
+        <v>0.3017367284028438</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1.675581171002939</v>
+        <v>1.676998138977815</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.1534181486947759</v>
+        <v>0.1579916673300943</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.68464531462633</v>
+        <v>-0.6787155286304198</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-1.549678227067815</v>
+        <v>-1.542931493237411</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-1.473523786755912</v>
+        <v>-1.467009539779752</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-2.543711527637285</v>
+        <v>-2.5366042366377</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-2.074466696816984</v>
+        <v>-2.068516430962632</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-3.334439908675414</v>
+        <v>-3.326187940295043</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-3.348861563320959</v>
+        <v>-3.341236486891319</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-3.589440309801283</v>
+        <v>-3.51540282304218</v>
       </c>
     </row>
     <row r="16">
@@ -4428,49 +4428,49 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>1.037313388218273</v>
+        <v>1.009220540027101</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-1.293461781198552</v>
+        <v>-1.320651857842677</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.2529710712557929</v>
+        <v>0.2243726922546827</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.4883489683505431</v>
+        <v>-0.5163441822553594</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.8421416814202587</v>
+        <v>0.8128246392170695</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.5709726381783682</v>
+        <v>-0.5990871174714627</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-1.377262698588453</v>
+        <v>-1.404835223101394</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-2.490768175382769</v>
+        <v>-2.517763943909955</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-1.900376345961405</v>
+        <v>-1.927882299709545</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-2.939092396860289</v>
+        <v>-2.966278985460271</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-3.026680796483973</v>
+        <v>-3.053935828079268</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-3.104662324054608</v>
+        <v>-3.131867538635724</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-3.560825473838825</v>
+        <v>-3.587930567055253</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-3.807190454234423</v>
+        <v>-3.781303892203219</v>
       </c>
     </row>
     <row r="17">
@@ -4480,101 +4480,101 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1539</v>
+        <v>1540</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.7537475985604871</v>
+        <v>-0.7745412720024802</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.9779971040317363</v>
+        <v>-0.9993186184435388</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.1772999946095339</v>
+        <v>-0.1993170931372319</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.7221129816629954</v>
+        <v>-0.7437451389584098</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.3214854147419501</v>
+        <v>-0.3436144833867019</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.8937354205896426</v>
+        <v>-0.9153933455898127</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.719920061947356</v>
+        <v>-1.741097776903395</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-2.670614515460343</v>
+        <v>-2.691386875754439</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-2.438549693491666</v>
+        <v>-2.459515986312482</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-3.060039120844117</v>
+        <v>-3.080969232732045</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-3.100710986114386</v>
+        <v>-3.121717523454066</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-2.90203341519986</v>
+        <v>-2.923173853926926</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-2.638299723726867</v>
+        <v>-2.659802713083231</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-2.678360084741037</v>
+        <v>-2.658748286888994</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; 49.48</t>
+          <t>X &lt; 49.49</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1758</v>
+        <v>1759</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-1.561761301576439</v>
+        <v>-1.577981493288306</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-1.449644701535817</v>
+        <v>-1.466466889267288</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-1.079869333948324</v>
+        <v>-1.097042999878639</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-1.824378638385042</v>
+        <v>-1.841102858829302</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-1.314387148947439</v>
+        <v>-1.33158950157096</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-2.062475414191411</v>
+        <v>-2.07917113214171</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-2.457380161848768</v>
+        <v>-2.473893726540332</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-2.951639546832119</v>
+        <v>-2.968039775131068</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-2.983024637578382</v>
+        <v>-2.999440694059658</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-3.292718211284409</v>
+        <v>-3.309251217925677</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-3.126783897464286</v>
+        <v>-3.143492107953065</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-2.834928229665081</v>
+        <v>-2.851804783028498</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-2.485763232361492</v>
+        <v>-2.502990430622013</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-2.603403384432568</v>
+        <v>-2.587574435158004</v>
       </c>
     </row>
     <row r="19">
@@ -4584,49 +4584,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1953</v>
+        <v>1954</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-1.628738421939374</v>
+        <v>-1.642075156106294</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-1.738599719433779</v>
+        <v>-1.752325928277742</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-1.903139295575301</v>
+        <v>-1.916898953645841</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-2.153631582558127</v>
+        <v>-2.167238996129413</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-1.849944746700331</v>
+        <v>-1.863863032481028</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-2.137378839593772</v>
+        <v>-2.151080707797327</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-2.909626216077818</v>
+        <v>-2.922967771204029</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-3.044096131303576</v>
+        <v>-3.057506156584495</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-3.027405298502593</v>
+        <v>-3.04085082625955</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-3.544267265089914</v>
+        <v>-3.557690217981879</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-3.262042377901011</v>
+        <v>-3.275675712662022</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-2.893635507042426</v>
+        <v>-2.907458465577804</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-2.723639153999756</v>
+        <v>-2.737674225088419</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-2.855924665248466</v>
+        <v>-2.842586966121729</v>
       </c>
     </row>
     <row r="20">
@@ -4636,101 +4636,101 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2190</v>
+        <v>2191</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-1.699067008362491</v>
+        <v>-1.709591166650505</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-1.970588681584765</v>
+        <v>-1.981344066403445</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-2.478072370802174</v>
+        <v>-2.488690038780106</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-2.415082052617869</v>
+        <v>-2.425707883165586</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.838471641744356</v>
+        <v>-1.849483372406013</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-2.017340178514367</v>
+        <v>-2.02821418381437</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-2.94295087958001</v>
+        <v>-2.953429843487996</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-2.840119528988915</v>
+        <v>-2.850753906298849</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-2.786166155776414</v>
+        <v>-2.796845994977829</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-3.384496738420118</v>
+        <v>-3.395095780349692</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-3.246026555107342</v>
+        <v>-3.256740809136872</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-3.187449795690291</v>
+        <v>-3.198191109041801</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-3.127076123046393</v>
+        <v>-3.137943980721552</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-3.309529586374374</v>
+        <v>-3.298555763757165</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 55.94</t>
+          <t>X &lt; 55.95</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2397</v>
+        <v>2398</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-1.37310637000251</v>
+        <v>-1.381787038414892</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-1.469063406814747</v>
+        <v>-1.477994239780749</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-1.84207333080073</v>
+        <v>-1.850924981993735</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-2.105398176045746</v>
+        <v>-2.114123447821335</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-1.790841739691849</v>
+        <v>-1.799798740461299</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-1.887114061027106</v>
+        <v>-1.895984503354313</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-2.324292248880298</v>
+        <v>-2.333001898219287</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-2.644837675022217</v>
+        <v>-2.653502625055417</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-2.517445518645999</v>
+        <v>-2.52618022882487</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-2.804177918056226</v>
+        <v>-2.81294992239912</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-2.736735629434754</v>
+        <v>-2.745578071945559</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-2.680034145008591</v>
+        <v>-2.688900183369213</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-2.827743307665862</v>
+        <v>-2.836628499514347</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-2.889312534237291</v>
+        <v>-2.88036153602517</v>
       </c>
     </row>
     <row r="22">
@@ -4740,49 +4740,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2602</v>
+        <v>2603</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-1.327090327858166</v>
+        <v>-1.334127039708669</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-1.235845904100024</v>
+        <v>-1.243153748837187</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-1.533941106667108</v>
+        <v>-1.541196385170352</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-1.766258441313397</v>
+        <v>-1.773410706900336</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.518542785812663</v>
+        <v>-1.525872067937129</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-1.507158508657767</v>
+        <v>-1.514453968654415</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-2.069813479944656</v>
+        <v>-2.076910262817307</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-2.286757029407973</v>
+        <v>-2.293842699634062</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-2.404191220587904</v>
+        <v>-2.411245293199919</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-2.850318196649539</v>
+        <v>-2.857328615899327</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-2.573987708769366</v>
+        <v>-2.581138402237706</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-2.672590567327418</v>
+        <v>-2.679703126427434</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-2.803344053196852</v>
+        <v>-2.810471927619645</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-2.994106606509916</v>
+        <v>-2.986641676634086</v>
       </c>
     </row>
     <row r="23">
@@ -4792,49 +4792,49 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2774</v>
+        <v>2775</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-1.112024613715533</v>
+        <v>-1.117931812456874</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-1.197617819749965</v>
+        <v>-1.203691646382538</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-1.429862686449454</v>
+        <v>-1.43590437698208</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.531983829002407</v>
+        <v>-1.537976910545822</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-1.512432480769441</v>
+        <v>-1.518501136251359</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-1.23174265799215</v>
+        <v>-1.23788009375906</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.90857315191797</v>
+        <v>-1.914481292782789</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-2.176912389782245</v>
+        <v>-2.182784099476862</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-2.290814178983332</v>
+        <v>-2.296655983052943</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-2.725916790358347</v>
+        <v>-2.73170839972655</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-2.443328475431628</v>
+        <v>-2.449250257970753</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-2.569667553741574</v>
+        <v>-2.57554344348204</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-2.898507983935126</v>
+        <v>-2.90432000882479</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-3.098041963206867</v>
+        <v>-3.091648719789418</v>
       </c>
     </row>
     <row r="24">
@@ -4844,49 +4844,49 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2931</v>
+        <v>2932</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-1.032840494123022</v>
+        <v>-1.0377920916549</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-1.165834223354324</v>
+        <v>-1.170906471424267</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-1.406746717269122</v>
+        <v>-1.411780066287299</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-1.700467357554352</v>
+        <v>-1.705390716906265</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-1.608728994344332</v>
+        <v>-1.613741046048247</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-1.531328118306838</v>
+        <v>-1.536339398429547</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-1.836252686952086</v>
+        <v>-1.84117183170396</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-2.013051649977768</v>
+        <v>-2.017960998834532</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-2.055948854875801</v>
+        <v>-2.060852797205307</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-2.479100419824732</v>
+        <v>-2.483949566201851</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-2.461088049339317</v>
+        <v>-2.465967148898862</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-2.681114263201948</v>
+        <v>-2.68591790661393</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-2.946674841106066</v>
+        <v>-2.951433693802741</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-3.122160742228417</v>
+        <v>-3.116660088593427</v>
       </c>
     </row>
     <row r="25">
@@ -4896,101 +4896,101 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3100</v>
+        <v>3101</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.8712089594647097</v>
+        <v>-0.8752641358651161</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-1.084446380475008</v>
+        <v>-1.088568554693587</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-1.108688097180021</v>
+        <v>-1.112837518635992</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-1.250656446070074</v>
+        <v>-1.254751868461419</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-1.128698448835685</v>
+        <v>-1.132880040047048</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.9426531165661629</v>
+        <v>-0.9468723475371448</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.267596697479263</v>
+        <v>-1.271720836938229</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-1.588795632704972</v>
+        <v>-1.59285753562984</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-1.535923142633536</v>
+        <v>-1.540009529449577</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.885504641886939</v>
+        <v>-1.889551412569013</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.847206678956717</v>
+        <v>-1.851285208576769</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-2.278835386338187</v>
+        <v>-2.282774391125152</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-2.617192163115909</v>
+        <v>-2.621059418371857</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-2.640358869037506</v>
+        <v>-2.635881762893789</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 66.71</t>
+          <t>X &lt; 66.72</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3249</v>
+        <v>3250</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-1.052604475942658</v>
+        <v>-1.055847075584914</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-1.023135208243232</v>
+        <v>-1.026498199625152</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-1.279021744065297</v>
+        <v>-1.282335023225961</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-1.224490962210879</v>
+        <v>-1.227814008936633</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-1.071339084420885</v>
+        <v>-1.074747675454908</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.8187738093893344</v>
+        <v>-0.8222416046158969</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-1.194112000563607</v>
+        <v>-1.197472282493173</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-1.491248938976071</v>
+        <v>-1.49455173648721</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-1.320635034451058</v>
+        <v>-1.323996322762746</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-1.570113773505334</v>
+        <v>-1.573458349355349</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.665856170640161</v>
+        <v>-1.669187240325414</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-1.983791516485915</v>
+        <v>-1.987024414611525</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-2.141196826623968</v>
+        <v>-2.144411951273</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-2.151702309699147</v>
+        <v>-2.148058976199678</v>
       </c>
     </row>
     <row r="27">
@@ -5000,49 +5000,49 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3392</v>
+        <v>3393</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.9515880999456598</v>
+        <v>-0.9541984732824389</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.9028967745373322</v>
+        <v>-0.9056116683852622</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-1.047044906594216</v>
+        <v>-1.049740723394343</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-1.195024332560145</v>
+        <v>-1.197670991858601</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-1.159151339112881</v>
+        <v>-1.161839740317923</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-1.051783255108063</v>
+        <v>-1.054488322215462</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-1.297282249364926</v>
+        <v>-1.299921306315163</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-1.366173105988565</v>
+        <v>-1.368819207842066</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-1.293585606008193</v>
+        <v>-1.296257949508032</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-1.42111658073555</v>
+        <v>-1.423799923024148</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-1.550861795365037</v>
+        <v>-1.55351979626635</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.736063923670542</v>
+        <v>-1.738666997311284</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-1.87500171904955</v>
+        <v>-1.877588652082345</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-1.844976945726486</v>
+        <v>-1.842017125330244</v>
       </c>
     </row>
     <row r="28">
@@ -5052,49 +5052,49 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3533</v>
+        <v>3534</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.6321862051507523</v>
+        <v>-0.6342850747971127</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.7622756849372792</v>
+        <v>-0.7644089481892706</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-1.085659420809201</v>
+        <v>-1.087719770694541</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-1.194352316646807</v>
+        <v>-1.196377484403691</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-1.153108010773039</v>
+        <v>-1.155169360141109</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-1.00992900987989</v>
+        <v>-1.012018998332756</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-1.220764230605674</v>
+        <v>-1.222799522837576</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-1.390271851972308</v>
+        <v>-1.392280744385722</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-1.238221356004075</v>
+        <v>-1.240277011632742</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-1.422814931636815</v>
+        <v>-1.424856619710432</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-1.527271074381957</v>
+        <v>-1.529293320174631</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-1.816862137341559</v>
+        <v>-1.81880214415353</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-1.882157167923872</v>
+        <v>-1.884098184254526</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-1.815061899451209</v>
+        <v>-1.812644758272718</v>
       </c>
     </row>
     <row r="29">
@@ -5104,49 +5104,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3642</v>
+        <v>3643</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.7560922189787931</v>
+        <v>-0.7577212821754955</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.8209396835847471</v>
+        <v>-0.8226082795489376</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-1.091722961150509</v>
+        <v>-1.093332183777413</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-1.193285776604725</v>
+        <v>-1.194863530382158</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-1.087177727987346</v>
+        <v>-1.088804292449815</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.966771168081479</v>
+        <v>-0.9684211875955029</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-1.091613453285667</v>
+        <v>-1.093233151601225</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-1.407041444433261</v>
+        <v>-1.408592000623393</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-1.179103715464436</v>
+        <v>-1.180719784643252</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-1.411004978366392</v>
+        <v>-1.412588236782497</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-1.408717796787286</v>
+        <v>-1.410309785715391</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-1.606258436231293</v>
+        <v>-1.607795930968656</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-1.654666283327025</v>
+        <v>-1.656206177553457</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-1.55458536635377</v>
+        <v>-1.552624106375568</v>
       </c>
     </row>
     <row r="30">
@@ -5156,49 +5156,49 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3737</v>
+        <v>3738</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.5734383202099735</v>
+        <v>-0.5747576727630914</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.5974099059669769</v>
+        <v>-0.5987687902648418</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.8445978222681561</v>
+        <v>-0.8459025827730642</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-1.020281363581788</v>
+        <v>-1.02153630499965</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.7703017921767668</v>
+        <v>-0.7716392789494222</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.6186174654277039</v>
+        <v>-0.6199878070722349</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.7423490488006621</v>
+        <v>-0.7436894677853587</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-1.061535388684753</v>
+        <v>-1.062804429739913</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.9210117611011839</v>
+        <v>-0.9223207731551426</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-1.115081743769942</v>
+        <v>-1.116363566204768</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-1.14471245652922</v>
+        <v>-1.145992850560141</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-1.389780037391986</v>
+        <v>-1.390994657522512</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-1.367323508930419</v>
+        <v>-1.368556697732814</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-1.263361622669443</v>
+        <v>-1.261793182068715</v>
       </c>
     </row>
     <row r="31">
@@ -5208,49 +5208,49 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3847</v>
+        <v>3848</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.4468061958576399</v>
+        <v>-0.4477639973823244</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.3086916429436073</v>
+        <v>-0.3097187039090628</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.5859355905225101</v>
+        <v>-0.5868994218023005</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.8306075434609639</v>
+        <v>-0.8315058038524725</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.6290030790819685</v>
+        <v>-0.6299651410910485</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.4731229972305968</v>
+        <v>-0.4741199048229774</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.5957037607438451</v>
+        <v>-0.5966711346511673</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.8412158289411238</v>
+        <v>-0.8421296063795722</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.7583109103280847</v>
+        <v>-0.7592479650085195</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.8931763672655322</v>
+        <v>-0.8940963882639181</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.9537269714261001</v>
+        <v>-0.9546359917446168</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-1.164777777363412</v>
+        <v>-1.165631785100814</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-1.154918240345381</v>
+        <v>-1.155783954323567</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-1.150710462654651</v>
+        <v>-1.149514277654973</v>
       </c>
     </row>
     <row r="32">
@@ -5260,49 +5260,49 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3925</v>
+        <v>3926</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.3095886503267877</v>
+        <v>-0.3103143549821752</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.07910388135812241</v>
+        <v>-0.07991319520813533</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.3332139731041579</v>
+        <v>-0.3339652025366036</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.5958028565915328</v>
+        <v>-0.596485763138844</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.4596501457230318</v>
+        <v>-0.4603762914310749</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.4026230570853002</v>
+        <v>-0.4033595160851462</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.5752998100321918</v>
+        <v>-0.5759940542549202</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.6725722343309215</v>
+        <v>-0.6732493002305588</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.6179258223793198</v>
+        <v>-0.6186181030033922</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.716051618767807</v>
+        <v>-0.7167323937493322</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.7539623775678095</v>
+        <v>-0.7546370359875425</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.883693190194748</v>
+        <v>-0.8843346708098068</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.9077785892322225</v>
+        <v>-0.9084207845817787</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.9495842645583537</v>
+        <v>-0.9486702854202633</v>
       </c>
     </row>
     <row r="33">
@@ -5312,101 +5312,101 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3973</v>
+        <v>3974</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.1853600462511196</v>
+        <v>-0.1859574150339753</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.04806209442927667</v>
+        <v>0.04738608513237352</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.1575111618591762</v>
+        <v>-0.1581407605489531</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.3148948935554827</v>
+        <v>-0.3154837061303226</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.3123681597040999</v>
+        <v>-0.312964530966255</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.2524053275994547</v>
+        <v>-0.2530134110783067</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.3737324615911035</v>
+        <v>-0.3743114240804317</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.5005485298774488</v>
+        <v>-0.50110168524823</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.4221160441716947</v>
+        <v>-0.4226899636091375</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.4789796230284935</v>
+        <v>-0.4795500281430733</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.4685431411718426</v>
+        <v>-0.4691190028940966</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.5710631639132231</v>
+        <v>-0.5716131277018732</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.6250185911704449</v>
+        <v>-0.625560470644885</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.5625514106287284</v>
+        <v>-0.5618718367161151</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; 83.95</t>
+          <t>X &lt; 83.94</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4028</v>
+        <v>4029</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.05592285374127925</v>
+        <v>-0.05637372474514279</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.0781563836574577</v>
+        <v>0.07765783680765992</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.1052284981516038</v>
+        <v>-0.1056853895413354</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.308210964320331</v>
+        <v>-0.3086166737522262</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.2882815684083866</v>
+        <v>-0.2886972046361862</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.2994075773840592</v>
+        <v>-0.2998180373460997</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.3458981226099525</v>
+        <v>-0.3462980334182859</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.4029800235284995</v>
+        <v>-0.4033701527405782</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.3016294153202566</v>
+        <v>-0.3020454245983757</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.2948791305140048</v>
+        <v>-0.2953045929532294</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.2377176024770122</v>
+        <v>-0.2381592881054928</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.3383119427262145</v>
+        <v>-0.3387285965007791</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.3475698529523115</v>
+        <v>-0.3479881748133096</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.3073031622110918</v>
+        <v>-0.3068385932071394</v>
       </c>
     </row>
     <row r="35">
@@ -5416,49 +5416,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4073</v>
+        <v>4074</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.07053083122319492</v>
+        <v>-0.07083528671248018</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.06879467637289594</v>
+        <v>0.06844608981347022</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.06795115886974656</v>
+        <v>-0.06826885719042508</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.1692846220298421</v>
+        <v>-0.16957686623401</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.2044720441365158</v>
+        <v>-0.2047591277552385</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.1631674314200922</v>
+        <v>-0.1634629573092496</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.1610267763019166</v>
+        <v>-0.1613235001257962</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.173556016288245</v>
+        <v>-0.1738526951999333</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.1229843066185907</v>
+        <v>-0.1232939127190207</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.1011201515728999</v>
+        <v>-0.1014405091628845</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.04680268864312609</v>
+        <v>-0.04713779120650941</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.1213197522529157</v>
+        <v>-0.121636526188972</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.1350641277077642</v>
+        <v>-0.1353802800364008</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.1169830582299056</v>
+        <v>-0.1166855386406738</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/btc_daily_14days/rsi/rsi_21.xlsx
+++ b/workspaces/btc_daily_14days/rsi/rsi_21.xlsx
@@ -568,989 +568,989 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ 24.72</t>
+          <t>X ≈ 24.77</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>1.75514340211469</v>
+        <v>1.651169799994989</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>2.240341652484091</v>
+        <v>2.15073866996903</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>6.172595558227343</v>
+        <v>5.913606982699768</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-6.703694476650369</v>
+        <v>-6.424738489415759</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-2.922267705326163</v>
+        <v>-2.757260812703201</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-6.954148706630903</v>
+        <v>-6.644097683419204</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-7.04937498255822</v>
+        <v>-6.706037136716617</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-16.22554148665799</v>
+        <v>-15.49377593147839</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-9.779468134328091</v>
+        <v>-9.292168497872119</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-10.66927908217006</v>
+        <v>-10.11747158890722</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-10.88572141533896</v>
+        <v>-10.32397756688933</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-5.281459219266999</v>
+        <v>-6.103762530535029</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-10.0590932701678</v>
+        <v>-10.66602046116869</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-6.424982053122754</v>
+        <v>-8.33631662688942</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ 26.88</t>
+          <t>X ≈ 26.93</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>1.508098843637519</v>
+        <v>1.453254123262873</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-3.345693914548363</v>
+        <v>-3.289350312633189</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-2.135009406223745</v>
+        <v>-2.100372492990992</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-6.834268187181721</v>
+        <v>-6.721172026168425</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-7.380263002543337</v>
+        <v>-7.211297435096981</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-13.52435813008601</v>
+        <v>-13.2772113576148</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-15.22693211608629</v>
+        <v>-14.92536333917605</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-14.09513446955871</v>
+        <v>-13.80916940062382</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-7.712336723831427</v>
+        <v>-7.508375482219378</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-5.353250297293457</v>
+        <v>-5.161860288122632</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-15.24019700601044</v>
+        <v>-14.88381157920569</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-7.141302724622861</v>
+        <v>-6.896927344278623</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-5.037814477542838</v>
+        <v>-5.706876199187626</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-6.424982053122754</v>
+        <v>-7.04663408720689</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ 29.02</t>
+          <t>X ≈ 29.08</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-5.84418317486994</v>
+        <v>-6.148327847954583</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-4.95637361007487</v>
+        <v>-4.080179502525858</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.1739293093770229</v>
+        <v>0.3898980631264664</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-3.936261686332919</v>
+        <v>-3.129305804791628</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-3.198970480477193</v>
+        <v>-3.618543029314374</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-1.595653222558056</v>
+        <v>-2.129952123479633</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.3191877406897206</v>
+        <v>0.2438450587460039</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>1.128695019413286</v>
+        <v>0.9965110432761151</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-7.301077037746673</v>
+        <v>-7.566014116766212</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-8.739981550337326</v>
+        <v>-9.609276199507043</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-4.316893054338657</v>
+        <v>-6.15995317746215</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-6.87991749938594</v>
+        <v>-9.760207883052317</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-7.300068352699348</v>
+        <v>-10.15786402619304</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.5808262089675011</v>
+        <v>-3.813958903312191</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ 31.18</t>
+          <t>X ≈ 31.23</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>2.692804792995005</v>
+        <v>2.426860108103867</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.9963812416603162</v>
+        <v>-0.2455352075542194</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-4.109574887904103</v>
+        <v>-5.021990544895594</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-4.517158612030066</v>
+        <v>-5.989266515561368</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-2.070168842921404</v>
+        <v>-3.190338036251795</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-2.300573112481501</v>
+        <v>-4.015347026293171</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-5.917114713241219</v>
+        <v>-8.464317757266279</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-4.561107597161261</v>
+        <v>-7.834406242513346</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-6.975030930154091</v>
+        <v>-8.970836904818874</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-9.001420314719248</v>
+        <v>-11.99172619098938</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>1.382113821137672</v>
+        <v>-2.316601372858294</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-2.112919791212882</v>
+        <v>-4.455874043589759</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-1.356600056290993</v>
+        <v>-3.753636651934933</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-1.130864406063928</v>
+        <v>-3.505730546303845</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ 33.33</t>
+          <t>X ≈ 33.39</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>112</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-2.479578843446951</v>
+        <v>-2.501272939912091</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.5204628531422202</v>
+        <v>-0.5192819699490272</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-2.701159222638331</v>
+        <v>-2.692973269702208</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-1.67807693619303</v>
+        <v>-1.673150399658255</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-3.109223632146261</v>
+        <v>-2.162202736395592</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-5.490421031082199</v>
+        <v>-6.344975067815348</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-4.682274247491435</v>
+        <v>-4.624564086836259</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-6.042200034135519</v>
+        <v>-5.982310822528568</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-3.424610762086459</v>
+        <v>-4.237559788150811</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-6.060243844131008</v>
+        <v>-5.953594996938918</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-6.264945002391201</v>
+        <v>-6.159504499549882</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-6.230566850035878</v>
+        <v>-6.103187072509265</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-3.972146274777458</v>
+        <v>-3.822236710760428</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.7178750897347967</v>
+        <v>0.889873849301047</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ 35.48</t>
+          <t>X ≈ 35.53</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>117</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-9.337642398584819</v>
+        <v>-7.634553889665334</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-1.565376810520576</v>
+        <v>0.1431629926605282</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>2.778083756603856</v>
+        <v>4.009322433837497</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>2.908308900192218</v>
+        <v>4.139859460755432</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>5.788822765900129</v>
+        <v>6.208066074470359</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>3.522094231432462</v>
+        <v>5.62957812669481</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>5.146785581568196</v>
+        <v>6.422045340098606</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>3.825016083080605</v>
+        <v>5.100159295632842</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.5094703469468413</v>
+        <v>0.7949618478546938</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-1.359389143276502</v>
+        <v>-0.0364967571564776</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>1.854713117266925</v>
+        <v>3.175411786126183</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>1.889091269622249</v>
+        <v>3.234325565689446</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>1.468940416308449</v>
+        <v>2.837142159208476</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.01472564286634537</v>
+        <v>1.011973971401368</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ 37.64</t>
+          <t>X ≈ 37.69</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.7364044367409903</v>
+        <v>-1.076550977550127</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-4.092102123598181</v>
+        <v>-5.503061154075439</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-1.579896764167302</v>
+        <v>-1.909789398667996</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.2868809229043947</v>
+        <v>-0.07054099124734137</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.337620221674328</v>
+        <v>0.01075835940271475</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-1.109191795202079</v>
+        <v>-0.856932502606746</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-1.193902154468503</v>
+        <v>-0.9175571865099528</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-1.079575449417909</v>
+        <v>-1.953454787717313</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.6036284405710788</v>
+        <v>-0.2786322458514476</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-1.990476402270545</v>
+        <v>-2.81465452553558</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-1.613782211693533</v>
+        <v>-2.448853800952264</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-3.904985454687036</v>
+        <v>-4.676680677801528</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-5.487927005674862</v>
+        <v>-6.216313869857167</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-9.913354146146013</v>
+        <v>-9.967269007841679</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ 39.8</t>
+          <t>X ≈ 39.83</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>6.097212445889518</v>
+        <v>6.569365818745119</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-2.612812182769652</v>
+        <v>-1.467435294829897</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>5.868156077445597</v>
+        <v>5.177510364809244</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>5.406665244702737</v>
+        <v>5.30898901829525</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>7.826955573263838</v>
+        <v>8.342245571470372</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>4.574033744910629</v>
+        <v>4.507301142624748</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>6.856187290969906</v>
+        <v>7.383594343613872</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>5.205686694520445</v>
+        <v>6.068134278078418</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>3.961272585334818</v>
+        <v>4.857996051296126</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>2.519637812673857</v>
+        <v>3.448792062478574</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>1.723220678082171</v>
+        <v>2.657428030080688</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-1.792697027550673</v>
+        <v>-0.8121590237224723</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-1.621131904532717</v>
+        <v>-0.619675214394853</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.3797516746878955</v>
+        <v>1.394075529973314</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ 41.95</t>
+          <t>X ≈ 41.98</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>5.277570727800438</v>
+        <v>4.363949252173541</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>2.384581814225655</v>
+        <v>1.125178034028252</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.0827284306328977</v>
+        <v>-0.3259830026166313</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>2.120035573058978</v>
+        <v>1.406885598150694</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>2.61801545001498</v>
+        <v>1.451257059735319</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>2.397254764624279</v>
+        <v>1.474352505590723</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-2.35066802987506</v>
+        <v>-4.173588999404252</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-2.817736673661798</v>
+        <v>-3.582498825064263</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.2880452550550388</v>
+        <v>-0.951559724502502</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.4164400936929482</v>
+        <v>-0.1917867358859553</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.8245304946190615</v>
+        <v>-1.159845047548643</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-2.344556487341698</v>
+        <v>-2.402651130080422</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-2.764707340654986</v>
+        <v>-3.56085168498322</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-5.129645265557869</v>
+        <v>-5.450844256122934</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ 44.11</t>
+          <t>X ≈ 44.14</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>3.902062692870025</v>
+        <v>3.819748369962987</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.3686978682790283</v>
+        <v>0.1150329032929776</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.2315543594169327</v>
+        <v>0.2512325905942703</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-5.4204781519989</v>
+        <v>-4.61690712170769</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-4.363023024243525</v>
+        <v>-3.521549104323029</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-5.129478781842487</v>
+        <v>-4.305992381415507</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-5.746104034725676</v>
+        <v>-5.423808132777914</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-8.340832252980498</v>
+        <v>-7.475299730296413</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-4.678410154184121</v>
+        <v>-3.812710755426146</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-5.528328950514108</v>
+        <v>-4.638145196085112</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-8.924519470476433</v>
+        <v>-8.01688881822438</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-1.97524770109959</v>
+        <v>-1.609515731653133</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-5.054973022498103</v>
+        <v>-4.121075774619072</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-5.361152265888947</v>
+        <v>-4.930231970804641</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ 46.25</t>
+          <t>X ≈ 46.28</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-10.77878837095998</v>
+        <v>-10.74357291350925</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.8015148976784161</v>
+        <v>0.1065065505114831</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-2.571979891332035</v>
+        <v>-2.815671155204619</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-2.016222832849969</v>
+        <v>-2.686512760263284</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-6.80983153488183</v>
+        <v>-7.583467781942929</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-2.682670271204195</v>
+        <v>-3.515795604771647</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-3.618444460257592</v>
+        <v>-3.997668078472252</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-3.659981189150614</v>
+        <v>-4.46280410994423</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-5.423091005247862</v>
+        <v>-6.189143576697099</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-3.71981831221612</v>
+        <v>-4.484103269891285</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-3.498987555582694</v>
+        <v>-3.84436186088729</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-1.762481743652899</v>
+        <v>-2.098431410442238</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>2.498218466863385</v>
+        <v>2.147760873964408</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>3.575017946877345</v>
+        <v>3.240687592519762</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ 48.41</t>
+          <t>X ≈ 48.44</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-7.275436578479457</v>
+        <v>-6.623228809724786</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-4.777033630447498</v>
+        <v>-3.706935844375892</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-7.454910038033589</v>
+        <v>-7.017573344176526</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-9.607789917276278</v>
+        <v>-9.15220837805844</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-8.31959545210713</v>
+        <v>-7.834270282789085</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-10.30532644530319</v>
+        <v>-8.919988645409902</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-7.650310777172002</v>
+        <v>-6.271247637758421</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-4.921032388995371</v>
+        <v>-3.578654007119553</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-6.80849856378299</v>
+        <v>-5.168127868980193</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-4.918691332715483</v>
+        <v>-3.472208736031</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-3.29690847271084</v>
+        <v>-2.318883120218679</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-2.349288311223098</v>
+        <v>-1.355739007288172</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-1.399576150837866</v>
+        <v>-0.393430870503586</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-2.087082509743759</v>
+        <v>-1.049363384053827</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ 50.56</t>
+          <t>X ≈ 50.59</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-2.224505774124211</v>
+        <v>-3.541039659938534</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-4.348512380008323</v>
+        <v>-5.639680662620037</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-9.358668380147975</v>
+        <v>-10.67259390866671</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-5.125879133995738</v>
+        <v>-6.418998527245954</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-6.689809712732227</v>
+        <v>-7.939175503249423</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-2.802692093353436</v>
+        <v>-4.058142561750081</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-6.98996655518382</v>
+        <v>-8.242509991181727</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-3.867291609227095</v>
+        <v>-5.10009532888477</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-3.415453252929474</v>
+        <v>-5.652531855547224</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-5.803833587720753</v>
+        <v>-7.507288271413756</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-4.470073207519398</v>
+        <v>-6.165036966372639</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-3.410054029523053</v>
+        <v>-5.075942393956204</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-4.855845908477377</v>
+        <v>-5.986564238045801</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-5.14293077107159</v>
+        <v>-6.768447211081863</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ 52.72</t>
+          <t>X ≈ 52.75</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-2.269945566399336</v>
+        <v>-1.446282037653035</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-3.88113165946325</v>
+        <v>-2.60392720791527</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-7.229489542108588</v>
+        <v>-5.976388600485301</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-4.567618828899874</v>
+        <v>-3.29331306990882</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-1.730380955835329</v>
+        <v>-0.3783068917117021</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-1.011065997930295</v>
+        <v>-0.531053287786392</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-3.205480998546683</v>
+        <v>-2.719368951480043</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-1.140904072712978</v>
+        <v>-0.632010222501485</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.7799453009655153</v>
+        <v>0.1820809981487628</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-2.051805025565614</v>
+        <v>-1.492811412453456</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-3.100388040365893</v>
+        <v>-2.548015689776683</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-5.597655457630914</v>
+        <v>-5.043040441773492</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-6.439747239214356</v>
+        <v>-6.289262198124554</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-7.057893445527718</v>
+        <v>-6.465749251002897</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ 54.87</t>
+          <t>X ≈ 54.89</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>2.10845595014203</v>
+        <v>2.611839394625214</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>3.878912369155444</v>
+        <v>3.955491577761983</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>4.933416346719241</v>
+        <v>5.025168223593731</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>1.198907190790813</v>
+        <v>1.252613240418121</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.271749512063444</v>
+        <v>-1.187855412729036</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.4912836949886454</v>
+        <v>0.06053986218745422</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>4.254923820141322</v>
+        <v>4.877932553449902</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.559970910602047</v>
+        <v>0.0218558906275419</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.3452305077542945</v>
+        <v>0.9604930375884209</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>3.360046010941453</v>
+        <v>3.55129860311478</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>2.672253065241648</v>
+        <v>2.859353277529912</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>2.706631217596971</v>
+        <v>2.917520014894805</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.3541132145251069</v>
+        <v>0.5711425761358555</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>1.546032439630871</v>
+        <v>1.795797194248784</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 57.03</t>
+          <t>X ≈ 57.05</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.7735989573637312</v>
+        <v>-0.83547067656162</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>1.517653973962801</v>
+        <v>0.4521656354117027</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>2.09849234530531</v>
+        <v>1.015365446140009</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>2.228717488893672</v>
+        <v>1.145249487354747</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1.690427935797977</v>
+        <v>0.656000346402827</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>2.963411721530626</v>
+        <v>2.364192563786347</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.9274818500693485</v>
+        <v>0.389660876474764</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.923827840428942</v>
+        <v>1.359234814655906</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-1.06398358438657</v>
+        <v>-1.54855119161008</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-3.377317014862712</v>
+        <v>-3.807786470989598</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.6551889048302186</v>
+        <v>-1.141113521396449</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-2.572030264669962</v>
+        <v>-2.51835348259609</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-2.504376239934651</v>
+        <v>-2.913511409159973</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-4.229860101903242</v>
+        <v>-4.578342145230728</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 59.17</t>
+          <t>X ≈ 59.2</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>2.170246760163387</v>
+        <v>1.927757997598221</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.6037300305749298</v>
+        <v>0.9362968887738035</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.1642892823445194</v>
+        <v>1.725990853121743</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>2.038700472444447</v>
+        <v>3.631022823330511</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.406565824837301</v>
+        <v>0.1831938007217886</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>2.960575646658256</v>
+        <v>4.006275177528877</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.5502838920432467</v>
+        <v>1.578755182977972</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.4981801005806332</v>
+        <v>0.5212064462632711</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.5591622571034094</v>
+        <v>0.4842338371265384</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.8276857045961279</v>
+        <v>0.8438372089742856</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.4509915140191083</v>
+        <v>1.231412737769489</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.9980087105009972</v>
+        <v>0.1061475224715878</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-4.325136308000445</v>
+        <v>-2.655874309417612</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-4.680796006611125</v>
+        <v>-3.590261400064968</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 61.33</t>
+          <t>X ≈ 61.34</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.3853260076822096</v>
+        <v>0.6950163802411424</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.5889174102223862</v>
+        <v>-1.529186345940268</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.9836887949774891</v>
+        <v>-1.922924334254908</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-4.675119702344475</v>
+        <v>-5.639194139194146</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-3.302581229962527</v>
+        <v>-4.205366357069146</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-6.826863251282788</v>
+        <v>-7.778734684404057</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.5421468589566061</v>
+        <v>-1.429134363373109</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.9016125227342968</v>
+        <v>0.0281097993204753</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>2.114515716530057</v>
+        <v>1.273188472234878</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>1.901539595359438</v>
+        <v>1.090385532445616</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-2.761760289015406</v>
+        <v>-3.600934402269957</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-4.63821016213771</v>
+        <v>-5.465844587981998</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-3.784475665132724</v>
+        <v>-4.578951232494532</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-3.558740014906192</v>
+        <v>-3.688880729453523</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 63.48</t>
+          <t>X ≈ 63.49</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>169</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1.956953791950852</v>
+        <v>1.336042021266927</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.3457676988870233</v>
+        <v>0.9362968887737324</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>4.09300814845151</v>
+        <v>4.684570734778553</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>6.590097197365253</v>
+        <v>7.181318681318679</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>7.235239596932409</v>
+        <v>7.875501493029475</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>9.30776155556152</v>
+        <v>9.923434940842483</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>8.631335219964058</v>
+        <v>9.271062875285672</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>5.797402670851739</v>
+        <v>6.438366209576884</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>7.511568443323043</v>
+        <v>8.176541529434239</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>8.436797575987327</v>
+        <v>9.127860877613273</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>8.823812394058507</v>
+        <v>9.51543640640854</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>4.716178712094298</v>
+        <v>5.431591309453907</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>3.112595906118173</v>
+        <v>3.853001430227287</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>5.705195461670144</v>
+        <v>6.468910197568164</v>
       </c>
     </row>
     <row r="25">
@@ -1560,49 +1560,49 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-4.829909319124958</v>
+        <v>-4.537138851914015</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.2703139837843693</v>
+        <v>-0.03923485598878074</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-4.822443978151952</v>
+        <v>-5.162702574033368</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.6653731969795444</v>
+        <v>-0.9787644787644822</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.1386191291193128</v>
+        <v>-0.1166622683650544</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.778275037948951</v>
+        <v>1.507474601805157</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>0.3512827994881533</v>
+        <v>0.09546716122841303</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.5553550952988857</v>
+        <v>0.3053100765207475</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>3.178936697165362</v>
+        <v>2.971040170086582</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>5.013581659224698</v>
+        <v>4.849914291974379</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>2.124316742575246</v>
+        <v>1.943071141735579</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>4.172117713722592</v>
+        <v>4.028264906127575</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>7.778812497992988</v>
+        <v>7.687161033617805</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>8.00454814821952</v>
+        <v>7.936205895633101</v>
       </c>
     </row>
     <row r="26">
@@ -1612,153 +1612,153 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1.365237815619494</v>
+        <v>1.65655484177968</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>1.851953820457723</v>
+        <v>1.46226664551272</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>4.254385232905598</v>
+        <v>3.846306434975872</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.5104945186110115</v>
+        <v>-0.8849206349206398</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-3.146686169608806</v>
+        <v>-3.457503109205895</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-6.345815636477134</v>
+        <v>-5.962495368164667</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-3.63332319854058</v>
+        <v>-3.245373679612428</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>1.494013752078274</v>
+        <v>1.149904671115344</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.6648705023466093</v>
+        <v>-0.2759568269103383</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>1.981714197827031</v>
+        <v>2.372436814496901</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>1.077712340266174</v>
+        <v>1.47385192251636</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>3.909293289824177</v>
+        <v>4.309796437658918</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>4.188443135811589</v>
+        <v>4.609082955539613</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>5.113479485338786</v>
+        <v>5.552572261999465</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 69.94</t>
+          <t>X ≈ 69.95</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>7.093552054572029</v>
+        <v>6.775602460827301</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>2.645486528884128</v>
+        <v>3.049568232814302</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-2.004604004807121</v>
+        <v>-1.62988404121468</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-1.165159003062733</v>
+        <v>-0.7857142857142918</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.9942286980023951</v>
+        <v>-0.560677712380496</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.01236518978871715</v>
+        <v>-0.2878921935615679</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>0.6368746886785814</v>
+        <v>0.3657374314986939</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-1.957853529576248</v>
+        <v>-1.528666757456087</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0.1088238883690664</v>
+        <v>-0.1370679380214455</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-1.450314766116868</v>
+        <v>-1.675182233122186</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.9457960662210283</v>
+        <v>-1.165036966372519</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-3.748297346489778</v>
+        <v>-3.964013086150452</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-2.040788625335182</v>
+        <v>-2.216313869857174</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-1.105833116952539</v>
+        <v>-1.252983293556085</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ 72.1</t>
+          <t>X ≈ 72.11</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>109</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-4.774494012185727</v>
+        <v>-4.803689806538358</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-2.715955334607351</v>
+        <v>-2.717142121052007</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-1.275864334041245</v>
+        <v>-1.276017724045566</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-1.145639190452883</v>
+        <v>-1.146133682830886</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>1.068364834433019</v>
+        <v>1.116910754198791</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.4483076714075622</v>
+        <v>0.4722650803571753</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>3.115890890123097</v>
+        <v>3.163902569113418</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-1.93833371696644</v>
+        <v>-1.889086154572723</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0.7529777044924231</v>
+        <v>0.8262348142721194</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-1.014372284497931</v>
+        <v>-0.9150249592033575</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>2.450651327884032</v>
+        <v>2.550559363902707</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>5.237323058221001</v>
+        <v>5.361019679249246</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>5.734603397568193</v>
+        <v>5.883292945346021</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>6.877770240455227</v>
+        <v>7.04976900002189</v>
       </c>
     </row>
     <row r="29">
@@ -1771,46 +1771,46 @@
         <v>95</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>6.466452390518306</v>
+        <v>6.437256596165675</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>8.013161034296559</v>
+        <v>8.011974247851903</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>8.671021228488826</v>
+        <v>8.670867838484504</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>5.643351635235085</v>
+        <v>5.642857142857082</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>11.42085155582365</v>
+        <v>11.46939747558942</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>12.77085716440611</v>
+        <v>12.79481457335572</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>12.68614680513988</v>
+        <v>12.73415848413021</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>12.2190781613532</v>
+        <v>12.26832572374692</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>9.000201267988274</v>
+        <v>9.07345837776797</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>10.25554562955327</v>
+        <v>10.35489295484784</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>8.998212892345649</v>
+        <v>9.098120928364324</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>6.927327886806289</v>
+        <v>7.051024507834533</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>9.66507177033499</v>
+        <v>9.813761318112817</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>9.890807420561522</v>
+        <v>10.06280618012818</v>
       </c>
     </row>
     <row r="30">
@@ -1823,46 +1823,46 @@
         <v>110</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>3.882720333101986</v>
+        <v>3.853524538749355</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>9.544261512765473</v>
+        <v>9.543074726320818</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>8.240399218919514</v>
+        <v>8.240245828915192</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>5.643351635235142</v>
+        <v>5.642857142857139</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>4.195971173048541</v>
+        <v>4.244517092814313</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>4.493345202683649</v>
+        <v>4.517302611633262</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>4.40863484341746</v>
+        <v>4.45664652240778</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>6.66883892690344</v>
+        <v>6.718086489297157</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>4.789674952198908</v>
+        <v>4.862932061978604</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>6.667028883141668</v>
+        <v>6.766376208436242</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>5.553236815790612</v>
+        <v>5.653144851809287</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>6.496705877236778</v>
+        <v>6.620402498265022</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>6.07655502392339</v>
+        <v>6.225244571701218</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>2.665927037786261</v>
+        <v>2.837925797352923</v>
       </c>
     </row>
     <row r="31">
@@ -1872,205 +1872,205 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>6.493442943824626</v>
+        <v>5.931446616671423</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>11.29251326101712</v>
+        <v>10.84177602502202</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>12.17979315831344</v>
+        <v>13.04544063410999</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>11.0279670198505</v>
+        <v>11.87662337662334</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>7.925574902652265</v>
+        <v>8.789971638268852</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>3.094743804082185</v>
+        <v>3.867951962282518</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>0.4459308807134974</v>
+        <v>1.20989327565453</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>7.671169929234445</v>
+        <v>8.536268307478977</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>6.328136490660391</v>
+        <v>7.200594399640885</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>8.042320258433094</v>
+        <v>8.974168416228537</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>9.119670382224186</v>
+        <v>10.06872926739368</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>13.00020238073339</v>
+        <v>12.72429860216123</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>11.2980002453687</v>
+        <v>12.32914067559738</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>8.959633331492704</v>
+        <v>9.980782940210169</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X ≈ 80.72</t>
+          <t>X ≈ 80.7</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>10.01908396946565</v>
+        <v>10.75519429756206</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>10.49123120973525</v>
+        <v>11.21283353893684</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>14.26312649164678</v>
+        <v>12.85991187715265</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>22.72668496856854</v>
+        <v>21.15306122448985</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>11.7717287488061</v>
+        <v>10.45973045088481</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>12.06910277844118</v>
+        <v>10.73251596970377</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>16.15105908584172</v>
+        <v>14.75349253353953</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>13.60065710872166</v>
+        <v>12.24684344662558</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>15.62300828553219</v>
+        <v>14.25068716401936</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>18.93975615586899</v>
+        <v>17.50849123626554</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>22.90172166427546</v>
+        <v>21.3859834417908</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>25.01943314996418</v>
+        <v>25.52578283221691</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>22.51594896331731</v>
+        <v>21.04899225259181</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>31.07501794687725</v>
+        <v>29.46130242072969</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X ≈ 82.87</t>
+          <t>X ≈ 82.86</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>9.337265787647461</v>
+        <v>8.60099928622413</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>2.271534240038179</v>
+        <v>1.462266645512685</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>3.69494467346496</v>
+        <v>2.920380509049885</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.1888061806896602</v>
+        <v>-0.6534391534391517</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>1.468698445775786</v>
+        <v>0.7091635574607764</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-3.688472979134531</v>
+        <v>-4.573606479275831</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>1.681362116144705</v>
+        <v>0.9212929870542084</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>6.668838926903419</v>
+        <v>6.01101578222643</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>8.426038588562484</v>
+        <v>7.825895024941509</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>13.03066524677809</v>
+        <v>12.55762199968208</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>16.46232772488153</v>
+        <v>16.05718525584972</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>16.4967058772368</v>
+        <v>16.11535199321454</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>19.71291866028709</v>
+        <v>19.42389777035446</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>18.12047249233174</v>
+        <v>17.82109078051793</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ 85.02</t>
+          <t>X ≈ 85</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-1.369804919423245</v>
+        <v>-0.3361987814087257</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.758768790264881</v>
+        <v>0.2545371769136793</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>3.290904269424551</v>
+        <v>4.208625275555477</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>12.31001830190184</v>
+        <v>13.03416149068323</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>7.327284304361704</v>
+        <v>8.197086262774789</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>12.06910277844119</v>
+        <v>12.81769786855023</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>16.42883686361948</v>
+        <v>17.1048678662813</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>20.40621266427718</v>
+        <v>20.98686119285448</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>15.90078606330997</v>
+        <v>16.60206249676116</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>17.27308948920232</v>
+        <v>17.95214695942443</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>17.06838833094213</v>
+        <v>17.74800651188832</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>19.32498870551968</v>
+        <v>19.98008629273151</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>18.90483785220628</v>
+        <v>19.58492836616768</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>16.90835128021057</v>
+        <v>17.66006018470477</v>
       </c>
     </row>
   </sheetData>
@@ -2210,1041 +2210,1041 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; 23.64</t>
+          <t>X &gt; 23.7</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4074</v>
+        <v>4085</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.02189963709172815</v>
+        <v>-0.02109279121201979</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.141867528873675</v>
+        <v>0.1415170455344139</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.02965035945583594</v>
+        <v>0.02957466414245857</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.07163367328591619</v>
+        <v>-0.0714285714285765</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.1557755372580516</v>
+        <v>-0.1566020616023494</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.1634629573092496</v>
+        <v>-0.1636382408199566</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.03880450968227933</v>
+        <v>-0.03993216771930008</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.02679387167052738</v>
+        <v>-0.0279858202070784</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.04831677617531227</v>
+        <v>0.04630614510813302</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.07021226180327034</v>
+        <v>0.06747227548980561</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.07550140428037366</v>
+        <v>0.07273211386230827</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.1727697544783524</v>
+        <v>0.1691268348533939</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.1345583702703408</v>
+        <v>0.1303751728671116</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.2024111722086133</v>
+        <v>0.2219249071783054</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; 25.8</t>
+          <t>X &gt; 25.85</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4028</v>
+        <v>4037</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.04219357448087635</v>
+        <v>-0.04097602241785125</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.1179028293488216</v>
+        <v>0.1176273655807734</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.0405024407287442</v>
+        <v>-0.04038658215200996</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.004104856246044619</v>
+        <v>0.004112393660200553</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.1241820318630289</v>
+        <v>-0.1256801839573569</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.08591292144311069</v>
+        <v>-0.08658546567881586</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.04125662282822162</v>
+        <v>0.0393279359497285</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.1581967912613109</v>
+        <v>0.1559026923866824</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.1605506654213755</v>
+        <v>0.1573407705386671</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.192857892841694</v>
+        <v>0.1885714346404228</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.2006792219820852</v>
+        <v>0.1963491722413266</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.2350573743374085</v>
+        <v>0.2437115981773061</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.2509704793716665</v>
+        <v>0.2587445041610792</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.2780963977213347</v>
+        <v>0.3236825474149256</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; 27.95</t>
+          <t>X &gt; 28</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3966</v>
+        <v>3974</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.06642910900517052</v>
+        <v>-0.06466411984560239</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.1720488197980501</v>
+        <v>0.1716383353159117</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.007759265776464019</v>
+        <v>-0.00772953323834713</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.1110083178427459</v>
+        <v>0.1107286288009135</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.01074859258361727</v>
+        <v>-0.01335157630215633</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.1241686728422735</v>
+        <v>0.1225261174092367</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.2799423771934997</v>
+        <v>0.2765638570199158</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.3810174009866856</v>
+        <v>0.377291605788713</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.2836265651020753</v>
+        <v>0.2788657136498287</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.2795595337363963</v>
+        <v>0.2733920683933277</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.4420645790510562</v>
+        <v>0.4354156360916406</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.3503711227326534</v>
+        <v>0.3569124671694368</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.3336494171751738</v>
+        <v>0.3533177563782246</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.3828848152584854</v>
+        <v>0.4405245071484885</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; 30.1</t>
+          <t>X &gt; 30.16</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3889</v>
+        <v>3892</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.04796715303432109</v>
+        <v>0.06351173465206728</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.273588682770594</v>
+        <v>0.2612192866784682</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.004469192915259157</v>
+        <v>-0.0161070930795475</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.1911419743923872</v>
+        <v>0.1789924580801028</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.05237639722554377</v>
+        <v>0.06260569480447487</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.158220173471193</v>
+        <v>0.169983264313899</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.2791653411973058</v>
+        <v>0.2772532047738849</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.3662138071016656</v>
+        <v>0.364245358647409</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.4337994057858907</v>
+        <v>0.4441483822248884</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.4581413448635914</v>
+        <v>0.4816086146337852</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.5362892480587789</v>
+        <v>0.5743725329856275</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.4935267472899056</v>
+        <v>0.5700686513210727</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.4847927106388781</v>
+        <v>0.5747763653635474</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.4019657483686387</v>
+        <v>0.5301616190852201</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; 32.26</t>
+          <t>X &gt; 32.31</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3804</v>
+        <v>3801</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.01113147982494667</v>
+        <v>0.006930650204786559</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.2574379552454502</v>
+        <v>0.273351530555118</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.08725898376034991</v>
+        <v>0.1037391037410913</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.2963484806610168</v>
+        <v>0.3266671664729941</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.09980445858529663</v>
+        <v>0.1404846423251627</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.2131616638250122</v>
+        <v>0.2701845419895648</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.4176206000372815</v>
+        <v>0.4865357508264196</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.4763143116658952</v>
+        <v>0.5605298352866086</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.5993489795384903</v>
+        <v>0.6695531865187476</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.6695143051855013</v>
+        <v>0.7802335731477896</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.5173893824668454</v>
+        <v>0.643585536256289</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.5517675348221687</v>
+        <v>0.6903950878474845</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.5259384480702707</v>
+        <v>0.6784031963485901</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.4362166850475973</v>
+        <v>0.626785188422339</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; 34.41</t>
+          <t>X &gt; 34.46</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3692</v>
+        <v>3689</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.06375099707799592</v>
+        <v>0.08308104383262105</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.281036246290796</v>
+        <v>0.2974163047639777</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.1718480517767844</v>
+        <v>0.1886487773181287</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.3562443762968996</v>
+        <v>0.3873826903023954</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.1971530897234146</v>
+        <v>0.210395454582347</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.386184757495009</v>
+        <v>0.471024302439055</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.5723303028875577</v>
+        <v>0.6417114574727165</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.67405905888414</v>
+        <v>0.7591739539299596</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.7214192642248491</v>
+        <v>0.8185357436244658</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.8736673151322663</v>
+        <v>0.984676186281348</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.7231373378038128</v>
+        <v>0.8501309642883683</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.7575154901591361</v>
+        <v>0.8966518517292883</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.6623917224361904</v>
+        <v>0.8150450151602442</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.4276723347429012</v>
+        <v>0.6187976768966124</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; 36.56</t>
+          <t>X &gt; 36.61</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3575</v>
+        <v>3572</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.3714329627542341</v>
+        <v>0.335870317970155</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.3414643099682593</v>
+        <v>0.3024688348636673</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.08655306507335325</v>
+        <v>0.06350353156987154</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.2727222646057754</v>
+        <v>0.264471217138059</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.01415299123035396</v>
+        <v>0.01394319743594963</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.2835549928934213</v>
+        <v>0.3020571139065993</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.4226208574034658</v>
+        <v>0.4523780128290369</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.5709368290013472</v>
+        <v>0.6169860242045289</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.7617029242268245</v>
+        <v>0.8193079009047253</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.9467491628620053</v>
+        <v>1.018124460184545</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.6861039486577525</v>
+        <v>0.7739669508071074</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.7204821010130757</v>
+        <v>0.8200819120502985</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.6359955833640001</v>
+        <v>0.7488117100500489</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.4421508140101125</v>
+        <v>0.6059192820318202</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; 38.72</t>
+          <t>X &gt; 38.76</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3403</v>
+        <v>3397</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.4274270952000734</v>
+        <v>0.4086326749663485</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.5655528866868664</v>
+        <v>0.6015467707083388</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.1707815019318275</v>
+        <v>0.165159776136143</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.3010066455201894</v>
+        <v>0.2817297206610121</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.002196219359227314</v>
+        <v>0.01410726769083226</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.3539494823299307</v>
+        <v>0.3617636734855978</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.5043258112800402</v>
+        <v>0.5229516542433217</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.654359724061031</v>
+        <v>0.7494049650600871</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.7696925837004613</v>
+        <v>0.8758694333399077</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>1.095207228452011</v>
+        <v>1.215574069398862</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.8023485621107085</v>
+        <v>0.9399939250661333</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.9542700585741741</v>
+        <v>1.103253373111258</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.9455209096392494</v>
+        <v>1.107627422880121</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.9655557076765433</v>
+        <v>1.150608110624063</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; 40.87</t>
+          <t>X &gt; 40.91</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3234</v>
+        <v>3227</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.1311396108876011</v>
+        <v>0.08408212199380216</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.731645557292353</v>
+        <v>0.7105417974023283</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.1269477198559983</v>
+        <v>-0.09889340021167925</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.034198883225244</v>
+        <v>0.0168911459483283</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.4113262913917879</v>
+        <v>-0.4246232906117839</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.133419414186406</v>
+        <v>0.1433746527996149</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.1723948928917949</v>
+        <v>0.1615295107066004</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.4165198174414755</v>
+        <v>0.4692116018084178</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.6029093368618064</v>
+        <v>0.6660889793415947</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>1.020770379740355</v>
+        <v>1.097927010575326</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.7542263024943878</v>
+        <v>0.8495186235934042</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>1.097819049778593</v>
+        <v>1.204158271611945</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>1.079647169872729</v>
+        <v>1.198622603647628</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.9961682251703792</v>
+        <v>1.137782123239695</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; 43.03</t>
+          <t>X &gt; 43.06</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3041</v>
+        <v>3040</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.1954836069894625</v>
+        <v>-0.1791860205534306</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.6267403624261547</v>
+        <v>0.6850362131098677</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.1297541397244828</v>
+        <v>-0.0849244016426951</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.0981807554258225</v>
+        <v>-0.06861180226280794</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.6035863887582806</v>
+        <v>-0.5400146147943161</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.01025708125407476</v>
+        <v>0.06150200198647582</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.332523516401821</v>
+        <v>0.428196340111441</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.6217850271695085</v>
+        <v>0.7184451050403879</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.6594546299364339</v>
+        <v>0.7655956594793736</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>1.05912478460953</v>
+        <v>1.177261375900407</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.8544236263493374</v>
+        <v>0.9731209283643167</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>1.316292735626739</v>
+        <v>1.426024507834477</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>1.323632839235387</v>
+        <v>1.491392897060116</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>1.384948890645738</v>
+        <v>1.543069338022853</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; 45.18</t>
+          <t>X &gt; 45.21</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2853</v>
+        <v>2851</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.4654936681088415</v>
+        <v>-0.4442854943547658</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.6923353106815284</v>
+        <v>0.7228231740202133</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.1230459584058039</v>
+        <v>-0.1072090987780072</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.2525349510430601</v>
+        <v>0.2329061968164936</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.3558562494413451</v>
+        <v>-0.3423611533699287</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.3270768408316655</v>
+        <v>0.3510342497812786</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.7330780132864945</v>
+        <v>0.8161405159711776</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1.212381609247394</v>
+        <v>1.261629171641111</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>1.01119615794719</v>
+        <v>1.069103169972934</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>1.493208662002885</v>
+        <v>1.56277938435543</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>1.498812445908833</v>
+        <v>1.569091409635895</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>1.533190598264156</v>
+        <v>1.627258147000788</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>1.743954571449166</v>
+        <v>1.863457638886622</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>1.829486926898284</v>
+        <v>1.972200852357616</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; 47.33</t>
+          <t>X &gt; 47.36</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2618</v>
+        <v>2614</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.4602604400538866</v>
+        <v>0.489506058185242</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.6825350039801279</v>
+        <v>0.7787019191508904</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.09677813412195491</v>
+        <v>0.138355364639402</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.456185859834072</v>
+        <v>0.4975972040192147</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.2234730829033893</v>
+        <v>0.314158460620817</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.5972413065797326</v>
+        <v>0.7016228785223078</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>1.123684499643588</v>
+        <v>1.252587584403884</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1.649740378393126</v>
+        <v>1.780638616069474</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>1.58875822187035</v>
+        <v>1.727176803852352</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>1.961146530200544</v>
+        <v>2.111023909625693</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>1.947430857043486</v>
+        <v>2.059905650306895</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>1.829020621316303</v>
+        <v>1.965050199454495</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>1.676249447147278</v>
+        <v>1.837681102270928</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>1.672802515250048</v>
+        <v>1.857192681960363</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; 49.49</t>
+          <t>X &gt; 49.52</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2399</v>
+        <v>2393</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1.166437033242218</v>
+        <v>1.146386294628265</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>1.180928305747379</v>
+        <v>1.192962657027785</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.7861569209923402</v>
+        <v>0.7992246687130802</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>1.374906449741189</v>
+        <v>1.388782759238246</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>1.003353036703849</v>
+        <v>1.066687818035604</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1.592515311441069</v>
+        <v>1.590204636478425</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>1.924645302320783</v>
+        <v>1.947434046626142</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>2.249573323811248</v>
+        <v>2.275583735051825</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>2.355327307346826</v>
+        <v>2.363976775726975</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>2.589193421396295</v>
+        <v>2.626650493282241</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>2.426176298150693</v>
+        <v>2.464298595683466</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>2.210450240418481</v>
+        <v>2.271734033424465</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1.957035527163427</v>
+        <v>2.043730306609902</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>2.016035037331605</v>
+        <v>2.125620968876007</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; 51.64</t>
+          <t>X &gt; 51.67</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2204</v>
+        <v>2199</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>1.466452390518278</v>
+        <v>1.559920007764212</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>1.670148330122323</v>
+        <v>1.795751562899405</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1.683725402717556</v>
+        <v>1.811290518650182</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>1.950066698756018</v>
+        <v>2.077600207886697</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1.684009450560495</v>
+        <v>1.861202362978432</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.981383480195582</v>
+        <v>2.088512665790084</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>2.713370035629957</v>
+        <v>2.846410464695595</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>2.79076600164359</v>
+        <v>2.926280296399568</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>2.865899997570907</v>
+        <v>3.071208551291875</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>3.331770674925252</v>
+        <v>3.520686018680621</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>3.036325415031669</v>
+        <v>3.225595139129979</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>2.707727160853416</v>
+        <v>2.919960148436665</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>2.559808612440179</v>
+        <v>2.752178301909218</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>2.649428110216633</v>
+        <v>2.910272731910027</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; 53.79</t>
+          <t>X &gt; 53.82</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1967</v>
+        <v>1964</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1.916643705103674</v>
+        <v>1.919623409328899</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>2.33901124701697</v>
+        <v>2.322189705028443</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>2.757661316252779</v>
+        <v>2.743115667833905</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>2.735369937217861</v>
+        <v>2.720250218213558</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>2.095402702373306</v>
+        <v>2.12916808337161</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>2.341937891133973</v>
+        <v>2.401953602190538</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>3.426520871979648</v>
+        <v>3.512376942700314</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>3.264485273439469</v>
+        <v>3.352043163987027</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>3.305180798665546</v>
+        <v>3.416903548740258</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>3.980427228568537</v>
+        <v>4.120569876275582</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>3.775726070308345</v>
+        <v>3.916429428739491</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>3.708426540914814</v>
+        <v>3.872763172214363</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>3.6441475737224</v>
+        <v>3.834020724265606</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>3.819044383074498</v>
+        <v>4.032149089335967</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 55.95</t>
+          <t>X &gt; 55.97</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1760</v>
+        <v>1759</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1.89408396946564</v>
+        <v>1.838950142139737</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>2.157897876401819</v>
+        <v>2.131839003544435</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>2.501762855283147</v>
+        <v>2.477157297208116</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>2.916078907962415</v>
+        <v>2.891293754568338</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>2.491425718503081</v>
+        <v>2.515745580074636</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>2.675163384501808</v>
+        <v>2.674830132435346</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>3.329089388871999</v>
+        <v>3.353230325188285</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>3.714293472357987</v>
+        <v>3.740154813241546</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>3.653311315835211</v>
+        <v>3.703182204104749</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>4.053392519505358</v>
+        <v>4.186914737559242</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>3.905509543063346</v>
+        <v>4.039624773252264</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>3.826251331782309</v>
+        <v>3.984090544158938</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>4.031100478468893</v>
+        <v>4.214287933115294</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>4.086381583240879</v>
+        <v>4.292781345443338</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 58.1</t>
+          <t>X &gt; 58.12</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1555</v>
+        <v>1550</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>2.245772072359543</v>
+        <v>2.199565594467856</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>2.242303021096355</v>
+        <v>2.358323993182978</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>2.554927134733596</v>
+        <v>2.674263424223106</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>3.006695686682086</v>
+        <v>3.126728110599075</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>2.59702349693044</v>
+        <v>2.766511227711675</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>2.63716279987743</v>
+        <v>2.716716101369308</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>3.645700029035694</v>
+        <v>3.752834205692231</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>3.950335565313267</v>
+        <v>4.061194993695985</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>4.27520549882265</v>
+        <v>4.41131915875274</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>5.033003744293431</v>
+        <v>5.264909932776476</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>4.506759177673111</v>
+        <v>4.738188840079083</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>4.669754693372489</v>
+        <v>4.860871706476232</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>4.89269065677933</v>
+        <v>5.175391199267253</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>5.182734988677893</v>
+        <v>5.488952190314876</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 60.25</t>
+          <t>X &gt; 60.27</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1383</v>
+        <v>1381</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>2.255164952835131</v>
+        <v>2.232828073737203</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>2.596256517038114</v>
+        <v>2.532344688798581</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>2.852244351372008</v>
+        <v>2.790308365943687</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>3.12708265475792</v>
+        <v>3.06501499948277</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>3.094939160953615</v>
+        <v>3.082644931666266</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>2.596940811702233</v>
+        <v>2.558906192700981</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>4.030668630310245</v>
+        <v>4.018887322881746</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>4.503585525207519</v>
+        <v>4.494401412607019</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>4.876442848077374</v>
+        <v>4.891896580443422</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>5.761881969318019</v>
+        <v>5.805939107521276</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>5.123341331665195</v>
+        <v>5.167330883011978</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>5.374639223716841</v>
+        <v>5.442731508863474</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>6.039087068884982</v>
+        <v>6.133743024732667</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>6.409435878909065</v>
+        <v>6.600021775234644</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 62.41</t>
+          <t>X &gt; 62.42</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>2.494614148910998</v>
+        <v>2.428663685317105</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>3.004145837250107</v>
+        <v>3.049568232814302</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>3.343469069134549</v>
+        <v>3.390524122050614</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>4.126222760846886</v>
+        <v>4.173469387755098</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>3.91419748181319</v>
+        <v>4.010750859048073</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>3.803741168870786</v>
+        <v>3.875373112560887</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>4.616257563275084</v>
+        <v>4.71267620700889</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>4.964849604643319</v>
+        <v>5.063169977237791</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>5.230131722182534</v>
+        <v>5.352727980345897</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>6.256232501709121</v>
+        <v>6.406450419939077</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>6.133097411964428</v>
+        <v>6.283942625464213</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>6.656871975412741</v>
+        <v>6.831905281196448</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>7.297080012800791</v>
+        <v>7.497971844428541</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>7.685947800058322</v>
+        <v>7.910282012566363</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 64.56</t>
+          <t>X &gt; 64.57</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>2.58057876605978</v>
+        <v>2.603524538749383</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>3.429184536761326</v>
+        <v>3.387771696017772</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>3.223627910757472</v>
+        <v>3.183427647096998</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>3.732282571848202</v>
+        <v>3.692099567099561</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>3.383207777503685</v>
+        <v>3.392244365541586</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>2.923722772134042</v>
+        <v>2.907454126784756</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>3.974300965374965</v>
+        <v>3.983161673922929</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>4.831735632846517</v>
+        <v>4.843086489297164</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>4.865360855699329</v>
+        <v>4.900810849857329</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>5.907589646881291</v>
+        <v>5.970921662981745</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>5.702888488621099</v>
+        <v>5.766781215445654</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>6.96716257285911</v>
+        <v>7.056008558871149</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>7.966122410179565</v>
+        <v>8.081305177761884</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>8.002643301654921</v>
+        <v>8.140956100383299</v>
       </c>
     </row>
     <row r="26">
@@ -3257,150 +3257,150 @@
         <v>908</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>3.796617009113227</v>
+        <v>3.767421214760596</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>3.947545453494328</v>
+        <v>3.946358667049672</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>4.543963496052072</v>
+        <v>4.543810106047751</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>4.453924322459812</v>
+        <v>4.453429830081809</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>3.915634769364118</v>
+        <v>3.96418068912989</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>3.111687213096126</v>
+        <v>3.135644622045739</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>4.568827074094273</v>
+        <v>4.616838753084593</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>5.533476491981538</v>
+        <v>5.582724054375255</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>5.142097859687837</v>
+        <v>5.215354969467533</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>6.054293600802914</v>
+        <v>6.153640926097488</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>6.290121076903951</v>
+        <v>6.390029112922626</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>7.425820815162353</v>
+        <v>7.549517436190598</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>7.996859389161727</v>
+        <v>8.145548936939555</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>8.002330722207638</v>
+        <v>8.174329481774301</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 68.87</t>
+          <t>X &gt; 68.88</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>4.251110113256495</v>
+        <v>4.165280845270082</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>4.339270425421432</v>
+        <v>4.414564493098524</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>4.598093811908221</v>
+        <v>4.675276766563925</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>5.381913726738411</v>
+        <v>5.459611069558711</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>5.235781036387813</v>
+        <v>5.363032085674853</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>4.879560294781072</v>
+        <v>4.850477290357652</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>6.102039477998559</v>
+        <v>6.098721724692403</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>6.288565605453655</v>
+        <v>6.418229278445189</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>6.227583448930879</v>
+        <v>6.25036661695237</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>6.815573149333041</v>
+        <v>6.866328612053614</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>7.264466762314676</v>
+        <v>7.316638426297629</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>8.0831586401602</v>
+        <v>8.160145477798658</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>8.708759420833715</v>
+        <v>8.812107970082998</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>8.542338208315151</v>
+        <v>8.668482675030297</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 71.02</t>
+          <t>X &gt; 71.03</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>624</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>3.608827559209239</v>
+        <v>3.579631764856607</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>4.722000440504388</v>
+        <v>4.720813654059732</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>6.090049568569853</v>
+        <v>6.089896178565532</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>6.861300353183864</v>
+        <v>6.860805860805861</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>6.643523620600988</v>
+        <v>6.692069540366759</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>5.979359188697607</v>
+        <v>6.00331659764722</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>7.33695652173914</v>
+        <v>7.38496820072946</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>8.151939160003678</v>
+        <v>8.201186722397395</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>7.610187772711669</v>
+        <v>7.683444882491365</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>8.683345899458743</v>
+        <v>8.782693224753316</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>9.119670382224186</v>
+        <v>9.219578418242861</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>10.75661263714361</v>
+        <v>10.88030925817186</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>11.13774383511226</v>
+        <v>11.28643338289009</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>10.72245384431314</v>
+        <v>10.89445260387981</v>
       </c>
     </row>
     <row r="29">
@@ -3413,46 +3413,46 @@
         <v>515</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>5.383161639368559</v>
+        <v>5.353965845015928</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>6.296247390964929</v>
+        <v>6.295060604520273</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>7.649048821743861</v>
+        <v>7.64889543173954</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>8.555972994458436</v>
+        <v>8.555478502080433</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>7.823508684081197</v>
+        <v>7.872054603846969</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>7.150008927308512</v>
+        <v>7.173966336258125</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>8.23034711173166</v>
+        <v>8.278358790721981</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>10.28755031260513</v>
+        <v>10.33679787499884</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>9.061519612393028</v>
+        <v>9.134776722172724</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>10.73587266072336</v>
+        <v>10.83521998601793</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>10.53117150246317</v>
+        <v>10.63107953848184</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>11.92477295578937</v>
+        <v>12.04846957681762</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>12.28132113160217</v>
+        <v>12.43001067938</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>11.53618299542094</v>
+        <v>11.7081817549876</v>
       </c>
     </row>
     <row r="30">
@@ -3465,46 +3465,46 @@
         <v>420</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>5.138131588513261</v>
+        <v>5.108935794160629</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>5.907897876401819</v>
+        <v>5.906711089957163</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>7.417888396408685</v>
+        <v>7.417735006404364</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>9.214780206663711</v>
+        <v>9.214285714285708</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>7.009823986901353</v>
+        <v>7.058369906667124</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>5.878626587965009</v>
+        <v>5.902583996914622</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>7.222487657270271</v>
+        <v>7.270499336260592</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>9.850657108721627</v>
+        <v>9.899904671115344</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>9.075389237913143</v>
+        <v>9.148646347692839</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>10.84451806063089</v>
+        <v>10.94386538592546</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>10.87791214046594</v>
+        <v>10.97782017648461</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>13.0551474356784</v>
+        <v>13.17884405670664</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>12.87309182046023</v>
+        <v>13.02178136823806</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>11.90835128021057</v>
+        <v>12.08035003977724</v>
       </c>
     </row>
     <row r="31">
@@ -3517,254 +3517,254 @@
         <v>310</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>5.583600098497911</v>
+        <v>5.55440430414528</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>4.617575295756652</v>
+        <v>4.616388509311996</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>7.126029717453228</v>
+        <v>7.125876327448907</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>10.4820613126545</v>
+        <v>10.4815668202765</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>8.008287888591063</v>
+        <v>8.056833808356835</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>6.370178047258399</v>
+        <v>6.394135456208012</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>8.220951558959982</v>
+        <v>8.268963237950302</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>10.97968936678614</v>
+        <v>11.02893692917986</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>10.59612656510208</v>
+        <v>10.66938367488178</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>12.32685293006254</v>
+        <v>12.42620025535712</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>12.76731306212493</v>
+        <v>12.8672210981436</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>15.38233637577058</v>
+        <v>15.50603299679883</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>15.28476616761846</v>
+        <v>15.43345571539628</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>15.18792117268371</v>
+        <v>15.35991993225037</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; 79.64</t>
+          <t>X &gt; 79.63</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>5.277704659120822</v>
+        <v>5.429802338203153</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>2.373415117781136</v>
+        <v>2.559071604978627</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>5.426919595095058</v>
+        <v>5.169625462157477</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>10.29852404902825</v>
+        <v>10.02053954629062</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>8.036096564898067</v>
+        <v>7.814552207913806</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>7.471401629015915</v>
+        <v>7.22896862802029</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>10.83496713181871</v>
+        <v>10.60178893364461</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>12.09203641906645</v>
+        <v>11.85269437068616</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>12.03105426254368</v>
+        <v>11.81572176154936</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>13.76734236276555</v>
+        <v>13.56700047687171</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>13.99367568726397</v>
+        <v>13.79204457869186</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>16.18322625341239</v>
+        <v>16.42531861219408</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>16.62514436561622</v>
+        <v>16.45934523498648</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>17.28191449860137</v>
+        <v>17.13757464635807</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 81.79</t>
+          <t>X &gt; 81.78</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>184</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>4.040823099900429</v>
+        <v>4.011627305547798</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.255723963358335</v>
+        <v>0.2545371769136793</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>3.121822143820694</v>
+        <v>3.121668753816373</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>7.056395113496009</v>
+        <v>7.055900621118006</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>7.061583821269878</v>
+        <v>7.110129741035649</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>6.272001329165846</v>
+        <v>6.295958738115459</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>9.448160535117054</v>
+        <v>9.496172214107375</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>11.69848319567814</v>
+        <v>11.74773075807186</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>11.0940227782858</v>
+        <v>11.1672798880655</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>12.41801702543421</v>
+        <v>12.51736435072878</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>11.66983760630445</v>
+        <v>11.76974564232313</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>13.87812880213803</v>
+        <v>14.00182542316627</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>15.08841273143332</v>
+        <v>15.23710227921115</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>13.68371359905115</v>
+        <v>13.85571235861782</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; 83.94</t>
+          <t>X &gt; 83.93</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>1.782649860938513</v>
+        <v>2.105272790497629</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.6037300305749298</v>
+        <v>-0.2471350638889902</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>2.8774675769181</v>
+        <v>3.205280793950145</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>9.984436906552979</v>
+        <v>10.25824175824175</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>9.446147353457285</v>
+        <v>9.768992617289832</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>10.51871518154198</v>
+        <v>10.81100890533953</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>12.75958621762464</v>
+        <v>13.05804512380638</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>13.84290517073713</v>
+        <v>14.13067390188457</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>12.23153541731513</v>
+        <v>12.55523975428624</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>12.15681041943488</v>
+        <v>12.50064194270203</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>9.62652786582585</v>
+        <v>9.98880918747362</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>12.76168121197963</v>
+        <v>13.12389900176159</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>13.11672415711583</v>
+        <v>13.49797184442854</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>11.79207221044313</v>
+        <v>12.20855516798238</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 86.1</t>
+          <t>X &gt; 86.08</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>3.471464921846604</v>
+        <v>3.442269127493972</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.5206735521696118</v>
+        <v>-0.5218603386142675</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>2.655983634503919</v>
+        <v>2.655830244499597</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>8.738589730473237</v>
+        <v>8.738095238095234</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>10.58125255832993</v>
+        <v>10.6297984780957</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>9.688150397488826</v>
+        <v>9.712107806438439</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>10.79391622869885</v>
+        <v>10.84192790768917</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>10.32684758491211</v>
+        <v>10.37609514730583</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>10.26586542838933</v>
+        <v>10.33912253816903</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>9.415946632059473</v>
+        <v>9.515293957354046</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>5.639816902370704</v>
+        <v>5.739724938389379</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>9.245623626154604</v>
+        <v>9.369320247182849</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>10.01594896331737</v>
+        <v>10.1646385110952</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>9.051208423067727</v>
+        <v>9.22320718263439</v>
       </c>
     </row>
   </sheetData>
@@ -3904,1041 +3904,1041 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; 23.64</t>
+          <t>X &lt; 23.7</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>1.090512540894217</v>
+        <v>1.061316746541586</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-4.092102123598181</v>
+        <v>-4.093288910042837</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-2.105921127400833</v>
+        <v>-2.106074517405155</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>3.976684968568478</v>
+        <v>3.976190476190474</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>8.200300177377542</v>
+        <v>8.248846097143314</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>9.688150397488826</v>
+        <v>9.712107806438439</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>4.841535276317892</v>
+        <v>4.889546955308212</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>3.183990442054963</v>
+        <v>3.23323800444868</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>1.93253209505599</v>
+        <v>2.005789204835686</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>1.08261329872613</v>
+        <v>1.181960624020704</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.3125640500102449</v>
+        <v>-0.2126560139915696</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-5.040090659559688</v>
+        <v>-4.916394038531443</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-3.079289131920717</v>
+        <v>-2.93059958414289</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-6.424982053122754</v>
+        <v>-7.443459484032282</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; 25.8</t>
+          <t>X &lt; 25.85</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>1.306962757344429</v>
+        <v>1.277766962991798</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-1.819374850870908</v>
+        <v>-1.820561637315564</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.8161567946770774</v>
+        <v>0.816003404672756</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.1888061806896815</v>
+        <v>0.1883116883116784</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>4.195971173048541</v>
+        <v>4.244517092814313</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>3.73576944510787</v>
+        <v>3.759726854057483</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.6207560555386635</v>
+        <v>0.6687677345289842</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-3.634191376126857</v>
+        <v>-3.58494381373314</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-2.180022017498118</v>
+        <v>-2.106764907718421</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-3.029940813827977</v>
+        <v>-2.930593488533404</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-3.992217729663928</v>
+        <v>-3.892309693645252</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-5.08552868209695</v>
+        <v>-5.349294471431875</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-5.505679535410358</v>
+        <v>-5.744452397995701</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-6.424982053122754</v>
+        <v>-7.768134808707607</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; 27.95</t>
+          <t>X &lt; 28</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1.365237815619494</v>
+        <v>1.336042021266863</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-2.297230328726378</v>
+        <v>-2.298417115171034</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.1278991493788624</v>
+        <v>-0.1280525393831837</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-2.048956057072544</v>
+        <v>-2.049450549450547</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.4896774667548343</v>
+        <v>0.5382233865206061</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-1.777051067712641</v>
+        <v>-1.753093658763028</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-4.425863991081378</v>
+        <v>-4.377852312091058</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-6.944214686150168</v>
+        <v>-6.894967123756452</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-3.928273765749871</v>
+        <v>-3.855016655970175</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-3.752551536438695</v>
+        <v>-3.653204211144121</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-7.546996284442486</v>
+        <v>-7.44708824842381</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-5.715102932510106</v>
+        <v>-5.850459972597378</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-5.355380915784515</v>
+        <v>-5.732797386340692</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-6.424982053122754</v>
+        <v>-7.535034575607376</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; 30.1</t>
+          <t>X &lt; 30.16</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.6693218276358053</v>
+        <v>-0.8855630884248882</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-3.005145601859049</v>
+        <v>-2.829751003905656</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.1390474213967039</v>
+        <v>0.02560848070383059</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-2.545054161866311</v>
+        <v>-2.371583290355865</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.5471118309040364</v>
+        <v>-0.6947674493583165</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-1.699013163587786</v>
+        <v>-1.866025251839027</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-3.045910611128001</v>
+        <v>-3.009713832039218</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-4.603888345823826</v>
+        <v>-4.558579083397298</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-4.845361544151508</v>
+        <v>-4.956562522858995</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-5.144492928380096</v>
+        <v>-5.419380273349077</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-6.63259206121473</v>
+        <v>-7.067564042184799</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-6.046065005017432</v>
+        <v>-7.009397304819906</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-5.909976962608546</v>
+        <v>-7.043544401058824</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-4.752119599591154</v>
+        <v>-6.433488708718549</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; 32.26</t>
+          <t>X &lt; 32.31</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>354</v>
+        <v>368</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.1218236954930418</v>
+        <v>-0.06445965097393724</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-2.037307603050238</v>
+        <v>-2.191114996999353</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-1.062215974106643</v>
+        <v>-1.226157333140144</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-2.983021991138493</v>
+        <v>-3.270186335403729</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.9004475597338271</v>
+        <v>-1.313783302442609</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-1.83513294899894</v>
+        <v>-2.399693435797595</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-3.712745161619054</v>
+        <v>-4.362523438066532</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-4.593787335722816</v>
+        <v>-5.371834459319437</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-5.349600813817858</v>
+        <v>-5.952285329325797</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-6.060243844131008</v>
+        <v>-7.047853040575568</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-4.724328755892607</v>
+        <v>-5.893297835937744</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-5.1069713444179</v>
+        <v>-6.378609359442414</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-4.819731787856334</v>
+        <v>-6.230289025136678</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-3.882609171766816</v>
+        <v>-5.709505032686522</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; 34.41</t>
+          <t>X &lt; 34.46</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>466</v>
+        <v>480</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.4893017747691601</v>
+        <v>-0.6351118248869767</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-1.68120065609294</v>
+        <v>-1.801622243376165</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-1.44704122323791</v>
+        <v>-1.570360231690877</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-2.675976095857287</v>
+        <v>-2.898809523809533</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-1.421253707334238</v>
+        <v>-1.513058664761445</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-2.698829711010276</v>
+        <v>-3.32360647927586</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-3.942316530789732</v>
+        <v>-4.425929235167978</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-4.937478484498712</v>
+        <v>-5.51676199555132</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-4.891853710221532</v>
+        <v>-5.553734604688117</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-6.060243844131008</v>
+        <v>-6.794229852169771</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-5.092237113265398</v>
+        <v>-5.95670363303919</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-5.375865995335026</v>
+        <v>-6.315203562340969</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-4.616456461379258</v>
+        <v>-5.66869482223813</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-2.776913383594859</v>
+        <v>-4.169649960222756</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; 36.56</t>
+          <t>X &lt; 36.61</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>583</v>
+        <v>597</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-2.228815190198219</v>
+        <v>-2.008439584084307</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-1.655127333682209</v>
+        <v>-1.417703625761902</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.6148196362993517</v>
+        <v>-0.473648971936143</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-1.574186307429279</v>
+        <v>-1.514333492594368</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.003710730788100136</v>
+        <v>0.003106329664412044</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-1.467276240171323</v>
+        <v>-1.5635730344598</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-2.139901366135696</v>
+        <v>-2.293125444755496</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-3.196881091617932</v>
+        <v>-3.427854526209074</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-4.019848857324959</v>
+        <v>-4.300947536683658</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-5.123276212103754</v>
+        <v>-5.459224278033759</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-3.705218039933861</v>
+        <v>-4.158348003161827</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-3.922874542343564</v>
+        <v>-4.434629426332052</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-3.397293045815047</v>
+        <v>-3.993666951558083</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-2.222580680910063</v>
+        <v>-3.154155822869321</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; 38.72</t>
+          <t>X &lt; 38.76</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>755</v>
+        <v>772</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-1.894214596375285</v>
+        <v>-1.798598241445845</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-2.201619724641212</v>
+        <v>-2.346846477960042</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.831521027935473</v>
+        <v>-0.8000928750716412</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-1.284752939928254</v>
+        <v>-1.187673258177796</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.07888407166824152</v>
+        <v>0.004836979912980155</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-1.386554713913533</v>
+        <v>-1.404136880310787</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-1.926368735680612</v>
+        <v>-1.982257393857068</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-2.718331064734357</v>
+        <v>-3.094920684641444</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-2.973482942537991</v>
+        <v>-3.390625505938658</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-4.413340023314142</v>
+        <v>-4.861284617154674</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-3.23064421083447</v>
+        <v>-3.771764003888698</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-3.918809914765077</v>
+        <v>-4.489793903005044</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-3.872939925571508</v>
+        <v>-4.496853511328247</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-3.974650927294945</v>
+        <v>-4.698579148478366</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; 40.87</t>
+          <t>X &lt; 40.91</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>924</v>
+        <v>942</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.4510015006198174</v>
+        <v>-0.2855355537005408</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-2.275862807358862</v>
+        <v>-2.186509249025896</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.3794366520745882</v>
+        <v>0.2799222541848323</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.07399311851218471</v>
+        <v>-0.01392251815980217</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>1.482339681281999</v>
+        <v>1.509540205295053</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.3057183946632378</v>
+        <v>-0.3363183436826347</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.3321131304132265</v>
+        <v>-0.2910422295182542</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-1.278375149342892</v>
+        <v>-1.441558743518797</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-1.711939687198353</v>
+        <v>-1.902709507480623</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-3.150761085510325</v>
+        <v>-3.362805320533148</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-2.327512424181926</v>
+        <v>-2.612544919712931</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-3.530782832757261</v>
+        <v>-3.826912646823111</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-3.461528514160094</v>
+        <v>-3.797892418561922</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-3.178228806369511</v>
+        <v>-3.599055480392607</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; 43.03</t>
+          <t>X &lt; 43.06</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1117</v>
+        <v>1129</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.5279335269877663</v>
+        <v>0.4828459215918883</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-1.479170325546804</v>
+        <v>-1.628500177648476</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.3003605341999673</v>
+        <v>0.1784660593889313</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.3017367284028438</v>
+        <v>0.2203219315895382</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1.676998138977815</v>
+        <v>1.491636170919307</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.1579916673300943</v>
+        <v>-0.03616154535514227</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.6787155286304198</v>
+        <v>-0.9305588647976037</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-1.542931493237411</v>
+        <v>-1.790298329767268</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-1.467009539779752</v>
+        <v>-1.739009685594269</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-2.5366042366377</v>
+        <v>-2.827622026338638</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-2.068516430962632</v>
+        <v>-2.366450393934358</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-3.326187940295043</v>
+        <v>-3.586976329803392</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-3.341236486891319</v>
+        <v>-3.758665323713053</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-3.51540282304218</v>
+        <v>-3.905773373272659</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; 45.18</t>
+          <t>X &lt; 45.21</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1305</v>
+        <v>1318</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>1.009220540027101</v>
+        <v>0.958968114781193</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-1.320651857842677</v>
+        <v>-1.378356783346</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.2243726922546827</v>
+        <v>0.1886895420647789</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.5163441822553594</v>
+        <v>-0.4703504043126685</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.8128246392170695</v>
+        <v>0.7762495113391878</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.5990871174714627</v>
+        <v>-0.6461140321459453</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-1.404835223101394</v>
+        <v>-1.573038078705395</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-2.517763943909955</v>
+        <v>-2.603877477144863</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-1.927882299709545</v>
+        <v>-2.03570636464778</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-2.966278985460271</v>
+        <v>-3.086463841075471</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-3.053935828079268</v>
+        <v>-3.174877995895621</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-3.131867538635724</v>
+        <v>-3.303839925977329</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-3.587930567055253</v>
+        <v>-3.810595251856519</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-3.781303892203219</v>
+        <v>-4.052679803419522</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; 47.33</t>
+          <t>X &lt; 47.36</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1540</v>
+        <v>1555</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.7745412720024802</v>
+        <v>-0.8168210900627031</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.9993186184435388</v>
+        <v>-1.152112439454598</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.1993170931372319</v>
+        <v>-0.2670780492526816</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.7437451389584098</v>
+        <v>-0.8062791335344173</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.3436144833867019</v>
+        <v>-0.4929989123073284</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.9153933455898127</v>
+        <v>-1.082254781646121</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.741097776903395</v>
+        <v>-1.94195487619362</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-2.691386875754439</v>
+        <v>-2.887138305151488</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-2.459515986312482</v>
+        <v>-2.667536186898943</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-3.080969232732045</v>
+        <v>-3.298933722171903</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-3.121717523454066</v>
+        <v>-3.276718609504748</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-2.923173853926926</v>
+        <v>-3.120357704922853</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-2.659802713083231</v>
+        <v>-2.903056433206416</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-2.658748286888994</v>
+        <v>-2.941086187446764</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; 49.49</t>
+          <t>X &lt; 49.52</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1759</v>
+        <v>1776</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-1.577981493288306</v>
+        <v>-1.531911713092683</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-1.466466889267288</v>
+        <v>-1.464653563286689</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-1.097042999878639</v>
+        <v>-1.101464503281996</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-1.841102858829302</v>
+        <v>-1.837545992641175</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-1.33158950157096</v>
+        <v>-1.401013846834275</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-2.07917113214171</v>
+        <v>-2.051184954612175</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-2.473893726540332</v>
+        <v>-2.474980459695928</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-2.968039775131068</v>
+        <v>-2.967659863115856</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-2.999440694059658</v>
+        <v>-2.975361031788999</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-3.309251217925677</v>
+        <v>-3.320447080634182</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-3.143492107953065</v>
+        <v>-3.157729490262348</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-2.851804783028498</v>
+        <v>-2.901020960166235</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-2.502990430622013</v>
+        <v>-2.590942055402635</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-2.587574435158004</v>
+        <v>-2.705685996258786</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; 51.64</t>
+          <t>X &lt; 51.67</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1954</v>
+        <v>1970</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-1.642075156106294</v>
+        <v>-1.728467851109883</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-1.752325928277742</v>
+        <v>-1.873309091677548</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-1.916898953645841</v>
+        <v>-2.038768443031948</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-2.167238996129413</v>
+        <v>-2.286435786435796</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-1.863863032481028</v>
+        <v>-2.041945307847186</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-2.151080707797327</v>
+        <v>-2.248025083927011</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-2.922967771204029</v>
+        <v>-3.04093935150587</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-3.057506156584495</v>
+        <v>-3.177018405807729</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-3.04085082625955</v>
+        <v>-3.238333760806263</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-3.557690217981879</v>
+        <v>-3.731919821774632</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-3.275675712662022</v>
+        <v>-3.453430276053211</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-2.907458465577804</v>
+        <v>-3.114983819271323</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-2.737674225088419</v>
+        <v>-2.925163619802817</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-2.842586966121729</v>
+        <v>-3.105775171728673</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; 53.79</t>
+          <t>X &lt; 53.82</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2191</v>
+        <v>2205</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-1.709591166650505</v>
+        <v>-1.698569895220615</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-1.981344066403445</v>
+        <v>-1.950753952893535</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-2.488690038780106</v>
+        <v>-2.456340977779931</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-2.425707883165586</v>
+        <v>-2.393260238632699</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.849483372406013</v>
+        <v>-1.86536218779667</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-2.02821418381437</v>
+        <v>-2.065698661833466</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-2.953429843487996</v>
+        <v>-3.006776130888291</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-2.850753906298849</v>
+        <v>-2.906517762172768</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-2.796845994977829</v>
+        <v>-2.874624499107419</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-3.395095780349692</v>
+        <v>-3.493716799506423</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-3.256740809136872</v>
+        <v>-3.357065951879775</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-3.198191109041801</v>
+        <v>-3.320282100326168</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-3.137943980721552</v>
+        <v>-3.283533141972185</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-3.298555763757165</v>
+        <v>-3.46386764729759</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 55.95</t>
+          <t>X &lt; 55.97</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2398</v>
+        <v>2410</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-1.381787038414892</v>
+        <v>-1.333884008130894</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-1.477994239780749</v>
+        <v>-1.450844649101469</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-1.850924981993735</v>
+        <v>-1.822838546436849</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-2.114123447821335</v>
+        <v>-2.084415584415588</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-1.799798740461299</v>
+        <v>-1.807946359401107</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-1.895984503354313</v>
+        <v>-1.885434436265101</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-2.333001898219287</v>
+        <v>-2.338027566432629</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-2.653502625055417</v>
+        <v>-2.658042348752211</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-2.52618022882487</v>
+        <v>-2.549076219594959</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-2.81294992239912</v>
+        <v>-2.895444986110661</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-2.745578071945559</v>
+        <v>-2.82894082049603</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-2.688900183369213</v>
+        <v>-2.790120643601334</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-2.836628499514347</v>
+        <v>-2.955781784770963</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-2.88036153602517</v>
+        <v>-3.016468770734512</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 58.1</t>
+          <t>X &lt; 58.12</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2603</v>
+        <v>2619</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-1.334127039708669</v>
+        <v>-1.294306353762366</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-1.243153748837187</v>
+        <v>-1.29967431483189</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-1.541196385170352</v>
+        <v>-1.597293058053353</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-1.773410706900336</v>
+        <v>-1.827663967831342</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.525872067937129</v>
+        <v>-1.6119932157508</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-1.514453968654415</v>
+        <v>-1.54734077695381</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-2.076910262817307</v>
+        <v>-2.120934312598798</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-2.293842699634062</v>
+        <v>-2.33819056697989</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-2.411245293199919</v>
+        <v>-2.46938501119218</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-2.857328615899327</v>
+        <v>-2.968140133018672</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-2.581138402237706</v>
+        <v>-2.694403861872139</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-2.679703126427434</v>
+        <v>-2.768449778797788</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-2.810471927619645</v>
+        <v>-2.952409834960768</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-2.986641676634086</v>
+        <v>-3.141108532196789</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 60.25</t>
+          <t>X &lt; 60.27</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2775</v>
+        <v>2788</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-1.117931812456874</v>
+        <v>-1.099901185829509</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-1.203691646382538</v>
+        <v>-1.164717481471413</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-1.43590437698208</v>
+        <v>-1.396637473562969</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.537976910545822</v>
+        <v>-1.497957724905554</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-1.518501136251359</v>
+        <v>-1.503524640211332</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-1.23788009375906</v>
+        <v>-1.211660842652101</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.914481292782789</v>
+        <v>-1.897232157052301</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-2.182784099476862</v>
+        <v>-2.165234913709277</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-2.296655983052943</v>
+        <v>-2.290666219439281</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-2.73170839972655</v>
+        <v>-2.737400816830707</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-2.449250257970753</v>
+        <v>-2.456688704100941</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-2.57554344348204</v>
+        <v>-2.594325426140252</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-2.90432000882479</v>
+        <v>-2.934441206844319</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-3.091648719789418</v>
+        <v>-3.168334800012332</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 62.41</t>
+          <t>X &lt; 62.42</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2932</v>
+        <v>2944</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-1.0377920916549</v>
+        <v>-1.005208206354688</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-1.170906471424267</v>
+        <v>-1.183951968229579</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-1.411780066287299</v>
+        <v>-1.424421145396465</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-1.705390716906265</v>
+        <v>-1.716655382532167</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-1.613741046048247</v>
+        <v>-1.646256542625771</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-1.536339398429547</v>
+        <v>-1.558701330224359</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-1.84117183170396</v>
+        <v>-1.872486899236662</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-2.017960998834532</v>
+        <v>-2.049247871257542</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-2.060852797205307</v>
+        <v>-2.102140844091302</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-2.483949566201851</v>
+        <v>-2.534844958456517</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-2.465967148898862</v>
+        <v>-2.517259565626006</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-2.68591790661393</v>
+        <v>-2.746381430636958</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-2.951433693802741</v>
+        <v>-3.021552773568061</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-3.116660088593427</v>
+        <v>-3.19591807616478</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 64.56</t>
+          <t>X &lt; 64.57</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3101</v>
+        <v>3113</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.8752641358651161</v>
+        <v>-0.8786338978236401</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-1.088568554693587</v>
+        <v>-1.069288910042836</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-1.112837518635992</v>
+        <v>-1.093941110905554</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-1.254751868461419</v>
+        <v>-1.235144778372444</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-1.132880040047048</v>
+        <v>-1.130825053828289</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.9468723475371448</v>
+        <v>-0.9369515609804324</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.271720836938229</v>
+        <v>-1.2688779531167</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-1.59285753562984</v>
+        <v>-1.589354706890433</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-1.540009529449577</v>
+        <v>-1.545021754570527</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.889551412569013</v>
+        <v>-1.902507041775159</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.851285208576769</v>
+        <v>-1.864651857258281</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-2.282774391125152</v>
+        <v>-2.302696874272478</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-2.621059418371857</v>
+        <v>-2.64846360836529</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-2.635881762893789</v>
+        <v>-2.671229358445274</v>
       </c>
     </row>
     <row r="26">
@@ -4948,153 +4948,153 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3250</v>
+        <v>3261</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-1.055847075584914</v>
+        <v>-1.044015306866221</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-1.026498199625152</v>
+        <v>-1.022711458163826</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-1.282335023225961</v>
+        <v>-1.277980443589811</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-1.227814008936633</v>
+        <v>-1.223544569157532</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-1.074747675454908</v>
+        <v>-1.084924108186527</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.8222416046158969</v>
+        <v>-0.8262831388047687</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-1.197472282493173</v>
+        <v>-1.207089985881971</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-1.49455173648721</v>
+        <v>-1.503523550494698</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-1.323996322762746</v>
+        <v>-1.340374735327032</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-1.573458349355349</v>
+        <v>-1.596424849617442</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.669187240325414</v>
+        <v>-1.691997750686255</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-1.987024414611525</v>
+        <v>-2.015543229314098</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-2.144411951273</v>
+        <v>-2.179526622769501</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-2.148058976199678</v>
+        <v>-2.189812487055022</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 68.87</t>
+          <t>X &lt; 68.88</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3393</v>
+        <v>3405</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.9541984732824389</v>
+        <v>-0.9302405551385959</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.9056116683852622</v>
+        <v>-0.9179889393082803</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-1.049740723394343</v>
+        <v>-1.061968350348181</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-1.197670991858601</v>
+        <v>-1.209265843965703</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-1.161839740317923</v>
+        <v>-1.184997739160977</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-1.054488322215462</v>
+        <v>-1.042988254839877</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-1.299921306315163</v>
+        <v>-1.293113682217609</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-1.368819207842066</v>
+        <v>-1.391505472537546</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-1.296257949508032</v>
+        <v>-1.295425709282448</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-1.423799923024148</v>
+        <v>-1.428775662280259</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-1.55351979626635</v>
+        <v>-1.558229454635438</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.738666997311284</v>
+        <v>-1.748196909371593</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-1.877588652082345</v>
+        <v>-1.892515530791663</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-1.842017125330244</v>
+        <v>-1.862381237755798</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 71.02</t>
+          <t>X &lt; 71.03</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3534</v>
+        <v>3545</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.6342850747971127</v>
+        <v>-0.6270314426497734</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.7644089481892706</v>
+        <v>-0.7618298153000751</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-1.087719770694541</v>
+        <v>-1.084327235815358</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-1.196377484403691</v>
+        <v>-1.192585895117553</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-1.155169360141109</v>
+        <v>-1.160404378511217</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-1.012018998332756</v>
+        <v>-1.013234962247992</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-1.222799522837576</v>
+        <v>-1.227731036969779</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-1.392280744385722</v>
+        <v>-1.396913126688091</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-1.240277011632742</v>
+        <v>-1.249743994359484</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-1.424856619710432</v>
+        <v>-1.438495842589603</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-1.529293320174631</v>
+        <v>-1.542714531197781</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-1.81880214415353</v>
+        <v>-1.835655117645921</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-1.884098184254526</v>
+        <v>-1.905299447167629</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-1.812644758272718</v>
+        <v>-1.838314746306445</v>
       </c>
     </row>
     <row r="29">
@@ -5104,49 +5104,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3643</v>
+        <v>3654</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.7577212821754955</v>
+        <v>-0.7511808186148272</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.8226082795489376</v>
+        <v>-0.8199664877842423</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-1.093332183777413</v>
+        <v>-1.09002826261402</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-1.194863530382158</v>
+        <v>-1.191203992514033</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-1.088804292449815</v>
+        <v>-1.092638244341025</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.9684211875955029</v>
+        <v>-0.96901882225783</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-1.093233151601225</v>
+        <v>-1.096977673663837</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-1.408592000623393</v>
+        <v>-1.411570738720719</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-1.180719784643252</v>
+        <v>-1.18790149910371</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-1.412588236782497</v>
+        <v>-1.422897612330146</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-1.410309785715391</v>
+        <v>-1.420711016140096</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-1.607795930968656</v>
+        <v>-1.621093423755994</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-1.656206177553457</v>
+        <v>-1.673026787582401</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-1.552624106375568</v>
+        <v>-1.573180337891067</v>
       </c>
     </row>
     <row r="30">
@@ -5156,49 +5156,49 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3738</v>
+        <v>3749</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.5747576727630914</v>
+        <v>-0.5696546212718872</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.5987687902648418</v>
+        <v>-0.5968783809282385</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.8459025827730642</v>
+        <v>-0.8434098770809513</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-1.02153630499965</v>
+        <v>-1.018488959829746</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.7716392789494222</v>
+        <v>-0.7750774690899931</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.6199878070722349</v>
+        <v>-0.6209847065848777</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.7436894677853587</v>
+        <v>-0.7471486174896</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-1.062804429739913</v>
+        <v>-1.065474822892639</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.9223207731551426</v>
+        <v>-0.928224038181277</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-1.116363566204768</v>
+        <v>-1.124765423712539</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-1.145992850560141</v>
+        <v>-1.154375985562289</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-1.390994657522512</v>
+        <v>-1.401458338845011</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-1.368556697732814</v>
+        <v>-1.382028155571454</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-1.261793182068715</v>
+        <v>-1.278323384246939</v>
       </c>
     </row>
     <row r="31">
@@ -5208,257 +5208,257 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3848</v>
+        <v>3859</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.4477639973823244</v>
+        <v>-0.4439961224076399</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.3097187039090628</v>
+        <v>-0.3087371146411328</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.5868994218023005</v>
+        <v>-0.5852181128278247</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.8315058038524725</v>
+        <v>-0.8290994350699705</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.6299651410910485</v>
+        <v>-0.632327882272655</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.4741199048229774</v>
+        <v>-0.474821891740298</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.5966711346511673</v>
+        <v>-0.599084089453207</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.8421296063795722</v>
+        <v>-0.8439504388458516</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.7592479650085195</v>
+        <v>-0.7633619338806668</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.8940963882639181</v>
+        <v>-0.9000629697812883</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.9546359917446168</v>
+        <v>-0.9604797421363784</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-1.165631785100814</v>
+        <v>-1.172915295052704</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-1.155783954323567</v>
+        <v>-1.165240590804615</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-1.149514277654973</v>
+        <v>-1.160990549321838</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; 79.64</t>
+          <t>X &lt; 79.63</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3926</v>
+        <v>3936</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.3103143549821752</v>
+        <v>-0.3196838684423113</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.07991319520813533</v>
+        <v>-0.09126256759096663</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.3339652025366036</v>
+        <v>-0.3193045776076104</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.596485763138844</v>
+        <v>-0.5811671855767173</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.4603762914310749</v>
+        <v>-0.4484198814914819</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.4033595160851462</v>
+        <v>-0.3900364995598267</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.5759940542549202</v>
+        <v>-0.5637578766423275</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.6732493002305588</v>
+        <v>-0.6607244511576127</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.6186181030033922</v>
+        <v>-0.6077606556058228</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.7167323937493322</v>
+        <v>-0.7070894122374511</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.7546370359875425</v>
+        <v>-0.7448795660171044</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.8843346708098068</v>
+        <v>-0.9011820624256117</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.9084207845817787</v>
+        <v>-0.9013169541490527</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.9486702854202633</v>
+        <v>-0.9430239439625936</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 81.79</t>
+          <t>X &lt; 81.78</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3974</v>
+        <v>3985</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.1859574150339753</v>
+        <v>-0.1839487433462139</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.04738608513237352</v>
+        <v>0.04731654404773877</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.1581407605489531</v>
+        <v>-0.1576975690282083</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.3154837061303226</v>
+        <v>-0.3145896656535001</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.312964530966255</v>
+        <v>-0.3145943015499668</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.2530134110783067</v>
+        <v>-0.2535463740917763</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.3743114240804317</v>
+        <v>-0.3757455344331788</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.50110168524823</v>
+        <v>-0.5022501772935684</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.4226899636091375</v>
+        <v>-0.4252884893998967</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.4795500281430733</v>
+        <v>-0.4833332197639848</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.4691190028940966</v>
+        <v>-0.4729607376864635</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.5716131277018732</v>
+        <v>-0.5763961883755826</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.625560470644885</v>
+        <v>-0.6314812413717519</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.5618718367161151</v>
+        <v>-0.5691689899174435</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; 83.94</t>
+          <t>X &lt; 83.93</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4029</v>
+        <v>4039</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.05637372474514279</v>
+        <v>-0.06687391768066675</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.07765783680765992</v>
+        <v>0.06617788827855975</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.1056853895413354</v>
+        <v>-0.1166565279871747</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.3086166737522262</v>
+        <v>-0.3191087746533583</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.2886972046361862</v>
+        <v>-0.3009374526402411</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.2998180373460997</v>
+        <v>-0.3111898743833379</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.3462980334182859</v>
+        <v>-0.3584345902511927</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.4033701527405782</v>
+        <v>-0.4152992843852701</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.3020454245983757</v>
+        <v>-0.3151094810481538</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.2953045929532294</v>
+        <v>-0.3091527641987852</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.2381592881054928</v>
+        <v>-0.2521225675600505</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.3387285965007791</v>
+        <v>-0.3533438741449757</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.3479881748133096</v>
+        <v>-0.3634142941853113</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.3068385932071394</v>
+        <v>-0.3232977278220019</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 86.1</t>
+          <t>X &lt; 86.08</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4074</v>
+        <v>4085</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.07083528671248018</v>
+        <v>-0.06989708598996458</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.06844608981347022</v>
+        <v>0.06829273506333777</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.06826885719042508</v>
+        <v>-0.06808158585754143</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.16957686623401</v>
+        <v>-0.1691086691086738</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.2047591277552385</v>
+        <v>-0.205454040107476</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.1634629573092496</v>
+        <v>-0.1636382408199566</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.1613235001257962</v>
+        <v>-0.1621218060379732</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.1738526951999333</v>
+        <v>-0.1746492276869063</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.1232939127190207</v>
+        <v>-0.1248429991461464</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.1014405091628845</v>
+        <v>-0.1037187247547564</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.04713779120650941</v>
+        <v>-0.04957708378935166</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.121636526188972</v>
+        <v>-0.1244870628711041</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.1353802800364008</v>
+        <v>-0.1388367703536417</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.1166855386406738</v>
+        <v>-0.1207923510836295</v>
       </c>
     </row>
   </sheetData>
